--- a/Site-emprunt-multimédia/CPNV_MEDIA-JUNIOR-ENTREPRISE_Teams-2627-AJI - 0000_materiel_multimédia/Gestion de projet/2627_00_plannification_site_emprunt_multimédia_ex.xlsx
+++ b/Site-emprunt-multimédia/CPNV_MEDIA-JUNIOR-ENTREPRISE_Teams-2627-AJI - 0000_materiel_multimédia/Gestion de projet/2627_00_plannification_site_emprunt_multimédia_ex.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud.sharepoint.com/sites/CPNV_MEDIA-JUNIOR-ENTREPRISE_Teams-2526-AJI/Documents partages/2627_00_Materiel_Multimédia/Gestion de projet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{674C794A-CEA8-9A41-8ABB-6C4D56813BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{616C56D3-54A1-B042-A2E8-579B724173AA}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{674C794A-CEA8-9A41-8ABB-6C4D56813BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F83E6AA-7EF7-7E47-94FD-1151A333F2D0}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2720" windowWidth="31220" windowHeight="17580" tabRatio="697" activeTab="4" xr2:uid="{1F4898CD-21D0-4507-8500-B5A48A0F8004}"/>
+    <workbookView minimized="1" xWindow="2980" yWindow="2720" windowWidth="31220" windowHeight="17580" tabRatio="697" activeTab="4" xr2:uid="{1F4898CD-21D0-4507-8500-B5A48A0F8004}"/>
   </bookViews>
   <sheets>
     <sheet name="Marche à suivre" sheetId="8" r:id="rId1"/>
@@ -47,7 +47,6 @@
     <definedName name="Vues">Ressources!$B$8:$B$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -268,7 +267,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="277">
   <si>
     <t>Marche à suivre pour la planification et gestion du temps d'un projet</t>
   </si>
@@ -1128,6 +1127,24 @@
   <si>
     <t>PV, Planif, devis</t>
   </si>
+  <si>
+    <t>Repo Git Hub</t>
+  </si>
+  <si>
+    <t>Création du Repo et coup d'œil des fichiers</t>
+  </si>
+  <si>
+    <t>PV</t>
+  </si>
+  <si>
+    <t>mer 30 sept 26</t>
+  </si>
+  <si>
+    <t>Affichage</t>
+  </si>
+  <si>
+    <t>Tentative d'affichage</t>
+  </si>
 </sst>
 </file>
 
@@ -1149,7 +1166,7 @@
     <numFmt numFmtId="176" formatCode="ddd\ d"/>
     <numFmt numFmtId="177" formatCode="d\ mmm"/>
   </numFmts>
-  <fonts count="68" x14ac:knownFonts="1">
+  <fonts count="69" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1595,8 +1612,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1685,6 +1709,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -2591,7 +2621,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="470">
+  <cellXfs count="485">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3708,29 +3738,29 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="15" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -3771,11 +3801,44 @@
     <xf numFmtId="177" fontId="57" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="171" fontId="23" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="171" fontId="23" fillId="5" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="172" fontId="23" fillId="11" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="172" fontId="23" fillId="11" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="173" fontId="23" fillId="7" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
@@ -3794,6 +3857,21 @@
     </xf>
     <xf numFmtId="176" fontId="21" fillId="0" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3819,59 +3897,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="43" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="20" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="34" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="34" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="23" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="171" fontId="23" fillId="5" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="172" fontId="23" fillId="11" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="172" fontId="23" fillId="11" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="7" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="173" fontId="23" fillId="7" borderId="63" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -3879,6 +3909,53 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="165" fontId="68" fillId="16" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="68" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="68" fillId="16" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="68" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="68" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="16" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="20" fontId="68" fillId="16" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -5055,13 +5132,13 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.84827586206896555</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.15172413793103445</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
@@ -15986,16 +16063,16 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="420" t="s">
+      <c r="B16" s="424" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="420"/>
-      <c r="D16" s="420"/>
-      <c r="E16" s="420"/>
-      <c r="F16" s="420"/>
-      <c r="G16" s="420"/>
-      <c r="H16" s="420"/>
-      <c r="I16" s="420"/>
+      <c r="C16" s="424"/>
+      <c r="D16" s="424"/>
+      <c r="E16" s="424"/>
+      <c r="F16" s="424"/>
+      <c r="G16" s="424"/>
+      <c r="H16" s="424"/>
+      <c r="I16" s="424"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B17" s="23" t="s">
@@ -16100,39 +16177,39 @@
     </row>
     <row r="32" spans="1:12" ht="28.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="284"/>
-      <c r="C32" s="417" t="s">
+      <c r="C32" s="419" t="s">
         <v>33</v>
       </c>
-      <c r="D32" s="417"/>
-      <c r="E32" s="417"/>
-      <c r="F32" s="417"/>
-      <c r="G32" s="417"/>
-      <c r="H32" s="417"/>
-      <c r="I32" s="417"/>
+      <c r="D32" s="419"/>
+      <c r="E32" s="419"/>
+      <c r="F32" s="419"/>
+      <c r="G32" s="419"/>
+      <c r="H32" s="419"/>
+      <c r="I32" s="419"/>
     </row>
     <row r="33" spans="1:10" ht="27.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="284"/>
-      <c r="C33" s="417" t="s">
+      <c r="C33" s="419" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="417"/>
-      <c r="E33" s="417"/>
-      <c r="F33" s="417"/>
-      <c r="G33" s="417"/>
-      <c r="H33" s="417"/>
-      <c r="I33" s="417"/>
+      <c r="D33" s="419"/>
+      <c r="E33" s="419"/>
+      <c r="F33" s="419"/>
+      <c r="G33" s="419"/>
+      <c r="H33" s="419"/>
+      <c r="I33" s="419"/>
     </row>
     <row r="34" spans="1:10" ht="27.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="417" t="s">
+      <c r="B34" s="419" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="417"/>
-      <c r="D34" s="417"/>
-      <c r="E34" s="417"/>
-      <c r="F34" s="417"/>
-      <c r="G34" s="417"/>
-      <c r="H34" s="417"/>
-      <c r="I34" s="417"/>
+      <c r="C34" s="419"/>
+      <c r="D34" s="419"/>
+      <c r="E34" s="419"/>
+      <c r="F34" s="419"/>
+      <c r="G34" s="419"/>
+      <c r="H34" s="419"/>
+      <c r="I34" s="419"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
@@ -16149,42 +16226,42 @@
     </row>
     <row r="36" spans="1:10" ht="66.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="287"/>
-      <c r="B36" s="418" t="s">
+      <c r="B36" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="418"/>
-      <c r="D36" s="418"/>
-      <c r="E36" s="418"/>
-      <c r="F36" s="418"/>
-      <c r="G36" s="418"/>
-      <c r="H36" s="418"/>
-      <c r="I36" s="418"/>
+      <c r="C36" s="423"/>
+      <c r="D36" s="423"/>
+      <c r="E36" s="423"/>
+      <c r="F36" s="423"/>
+      <c r="G36" s="423"/>
+      <c r="H36" s="423"/>
+      <c r="I36" s="423"/>
     </row>
     <row r="37" spans="1:10" ht="42.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="286"/>
-      <c r="B37" s="419" t="s">
+      <c r="B37" s="420" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="419"/>
-      <c r="D37" s="419"/>
-      <c r="E37" s="419"/>
-      <c r="F37" s="419"/>
-      <c r="G37" s="419"/>
-      <c r="H37" s="419"/>
-      <c r="I37" s="419"/>
+      <c r="C37" s="420"/>
+      <c r="D37" s="420"/>
+      <c r="E37" s="420"/>
+      <c r="F37" s="420"/>
+      <c r="G37" s="420"/>
+      <c r="H37" s="420"/>
+      <c r="I37" s="420"/>
       <c r="J37" s="289"/>
     </row>
     <row r="38" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="419" t="s">
+      <c r="B38" s="420" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="419"/>
-      <c r="D38" s="419"/>
-      <c r="E38" s="419"/>
-      <c r="F38" s="419"/>
-      <c r="G38" s="419"/>
-      <c r="H38" s="419"/>
-      <c r="I38" s="419"/>
+      <c r="C38" s="420"/>
+      <c r="D38" s="420"/>
+      <c r="E38" s="420"/>
+      <c r="F38" s="420"/>
+      <c r="G38" s="420"/>
+      <c r="H38" s="420"/>
+      <c r="I38" s="420"/>
       <c r="J38" s="289"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -16201,55 +16278,55 @@
       <c r="I39" s="290"/>
     </row>
     <row r="40" spans="1:10" ht="56.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B40" s="422" t="s">
+      <c r="B40" s="418" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="422"/>
-      <c r="D40" s="422"/>
-      <c r="E40" s="422"/>
-      <c r="F40" s="422"/>
-      <c r="G40" s="422"/>
-      <c r="H40" s="422"/>
-      <c r="I40" s="422"/>
+      <c r="C40" s="418"/>
+      <c r="D40" s="418"/>
+      <c r="E40" s="418"/>
+      <c r="F40" s="418"/>
+      <c r="G40" s="418"/>
+      <c r="H40" s="418"/>
+      <c r="I40" s="418"/>
       <c r="J40" s="291"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="423" t="s">
+      <c r="B41" s="421" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="423"/>
-      <c r="D41" s="423"/>
-      <c r="E41" s="423"/>
-      <c r="F41" s="423"/>
-      <c r="G41" s="423"/>
-      <c r="H41" s="423"/>
-      <c r="I41" s="423"/>
-      <c r="J41" s="423"/>
+      <c r="C41" s="421"/>
+      <c r="D41" s="421"/>
+      <c r="E41" s="421"/>
+      <c r="F41" s="421"/>
+      <c r="G41" s="421"/>
+      <c r="H41" s="421"/>
+      <c r="I41" s="421"/>
+      <c r="J41" s="421"/>
     </row>
     <row r="42" spans="1:10" ht="43.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B42" s="419" t="s">
+      <c r="B42" s="420" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="419"/>
-      <c r="D42" s="419"/>
-      <c r="E42" s="419"/>
-      <c r="F42" s="419"/>
-      <c r="G42" s="419"/>
-      <c r="H42" s="419"/>
-      <c r="I42" s="419"/>
+      <c r="C42" s="420"/>
+      <c r="D42" s="420"/>
+      <c r="E42" s="420"/>
+      <c r="F42" s="420"/>
+      <c r="G42" s="420"/>
+      <c r="H42" s="420"/>
+      <c r="I42" s="420"/>
       <c r="J42" s="292"/>
     </row>
     <row r="43" spans="1:10" ht="25.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="419" t="s">
+      <c r="B43" s="420" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="419"/>
-      <c r="D43" s="419"/>
-      <c r="E43" s="419"/>
-      <c r="F43" s="419"/>
-      <c r="G43" s="419"/>
-      <c r="H43" s="419"/>
-      <c r="I43" s="419"/>
+      <c r="C43" s="420"/>
+      <c r="D43" s="420"/>
+      <c r="E43" s="420"/>
+      <c r="F43" s="420"/>
+      <c r="G43" s="420"/>
+      <c r="H43" s="420"/>
+      <c r="I43" s="420"/>
       <c r="J43" s="292"/>
     </row>
     <row r="44" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -16292,42 +16369,42 @@
       <c r="J46" s="288"/>
     </row>
     <row r="47" spans="1:10" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B47" s="417" t="s">
+      <c r="B47" s="419" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="417"/>
-      <c r="D47" s="417"/>
-      <c r="E47" s="417"/>
-      <c r="F47" s="417"/>
-      <c r="G47" s="417"/>
-      <c r="H47" s="417"/>
-      <c r="I47" s="417"/>
+      <c r="C47" s="419"/>
+      <c r="D47" s="419"/>
+      <c r="E47" s="419"/>
+      <c r="F47" s="419"/>
+      <c r="G47" s="419"/>
+      <c r="H47" s="419"/>
+      <c r="I47" s="419"/>
       <c r="J47" s="23"/>
     </row>
     <row r="48" spans="1:10" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B48" s="417" t="s">
+      <c r="B48" s="419" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="417"/>
-      <c r="D48" s="417"/>
-      <c r="E48" s="417"/>
-      <c r="F48" s="417"/>
-      <c r="G48" s="417"/>
-      <c r="H48" s="417"/>
-      <c r="I48" s="417"/>
+      <c r="C48" s="419"/>
+      <c r="D48" s="419"/>
+      <c r="E48" s="419"/>
+      <c r="F48" s="419"/>
+      <c r="G48" s="419"/>
+      <c r="H48" s="419"/>
+      <c r="I48" s="419"/>
       <c r="J48" s="23"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B49" s="419" t="s">
+      <c r="B49" s="420" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="419"/>
-      <c r="D49" s="419"/>
-      <c r="E49" s="419"/>
-      <c r="F49" s="419"/>
-      <c r="G49" s="419"/>
-      <c r="H49" s="419"/>
-      <c r="I49" s="419"/>
+      <c r="C49" s="420"/>
+      <c r="D49" s="420"/>
+      <c r="E49" s="420"/>
+      <c r="F49" s="420"/>
+      <c r="G49" s="420"/>
+      <c r="H49" s="420"/>
+      <c r="I49" s="420"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="20" t="s">
@@ -16405,16 +16482,16 @@
       </c>
     </row>
     <row r="63" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B63" s="417" t="s">
+      <c r="B63" s="419" t="s">
         <v>64</v>
       </c>
-      <c r="C63" s="417"/>
-      <c r="D63" s="417"/>
-      <c r="E63" s="417"/>
-      <c r="F63" s="417"/>
-      <c r="G63" s="417"/>
-      <c r="H63" s="417"/>
-      <c r="I63" s="417"/>
+      <c r="C63" s="419"/>
+      <c r="D63" s="419"/>
+      <c r="E63" s="419"/>
+      <c r="F63" s="419"/>
+      <c r="G63" s="419"/>
+      <c r="H63" s="419"/>
+      <c r="I63" s="419"/>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="20" t="s">
@@ -16427,16 +16504,16 @@
       </c>
     </row>
     <row r="66" spans="1:9" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B66" s="417" t="s">
+      <c r="B66" s="419" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="417"/>
-      <c r="D66" s="417"/>
-      <c r="E66" s="417"/>
-      <c r="F66" s="417"/>
-      <c r="G66" s="417"/>
-      <c r="H66" s="417"/>
-      <c r="I66" s="417"/>
+      <c r="C66" s="419"/>
+      <c r="D66" s="419"/>
+      <c r="E66" s="419"/>
+      <c r="F66" s="419"/>
+      <c r="G66" s="419"/>
+      <c r="H66" s="419"/>
+      <c r="I66" s="419"/>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="20" t="s">
@@ -16459,56 +16536,56 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A71" s="424" t="s">
+      <c r="A71" s="422" t="s">
         <v>72</v>
       </c>
-      <c r="B71" s="424"/>
-      <c r="C71" s="424"/>
-      <c r="D71" s="424"/>
-      <c r="E71" s="424"/>
-      <c r="F71" s="424"/>
-      <c r="G71" s="424"/>
-      <c r="H71" s="424"/>
-      <c r="I71" s="424"/>
+      <c r="B71" s="422"/>
+      <c r="C71" s="422"/>
+      <c r="D71" s="422"/>
+      <c r="E71" s="422"/>
+      <c r="F71" s="422"/>
+      <c r="G71" s="422"/>
+      <c r="H71" s="422"/>
+      <c r="I71" s="422"/>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A72" s="424" t="s">
+      <c r="A72" s="422" t="s">
         <v>73</v>
       </c>
-      <c r="B72" s="424"/>
-      <c r="C72" s="424"/>
-      <c r="D72" s="424"/>
-      <c r="E72" s="424"/>
-      <c r="F72" s="424"/>
-      <c r="G72" s="424"/>
-      <c r="H72" s="424"/>
-      <c r="I72" s="424"/>
+      <c r="B72" s="422"/>
+      <c r="C72" s="422"/>
+      <c r="D72" s="422"/>
+      <c r="E72" s="422"/>
+      <c r="F72" s="422"/>
+      <c r="G72" s="422"/>
+      <c r="H72" s="422"/>
+      <c r="I72" s="422"/>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A73" s="424" t="s">
+      <c r="A73" s="422" t="s">
         <v>74</v>
       </c>
-      <c r="B73" s="424"/>
-      <c r="C73" s="424"/>
-      <c r="D73" s="424"/>
-      <c r="E73" s="424"/>
-      <c r="F73" s="424"/>
-      <c r="G73" s="424"/>
-      <c r="H73" s="424"/>
-      <c r="I73" s="424"/>
+      <c r="B73" s="422"/>
+      <c r="C73" s="422"/>
+      <c r="D73" s="422"/>
+      <c r="E73" s="422"/>
+      <c r="F73" s="422"/>
+      <c r="G73" s="422"/>
+      <c r="H73" s="422"/>
+      <c r="I73" s="422"/>
     </row>
     <row r="74" spans="1:9" ht="26.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="421" t="s">
+      <c r="A74" s="417" t="s">
         <v>75</v>
       </c>
-      <c r="B74" s="421"/>
-      <c r="C74" s="421"/>
-      <c r="D74" s="421"/>
-      <c r="E74" s="421"/>
-      <c r="F74" s="421"/>
-      <c r="G74" s="421"/>
-      <c r="H74" s="421"/>
-      <c r="I74" s="421"/>
+      <c r="B74" s="417"/>
+      <c r="C74" s="417"/>
+      <c r="D74" s="417"/>
+      <c r="E74" s="417"/>
+      <c r="F74" s="417"/>
+      <c r="G74" s="417"/>
+      <c r="H74" s="417"/>
+      <c r="I74" s="417"/>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="385" t="s">
@@ -16525,6 +16602,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B16:I16"/>
+    <mergeCell ref="B34:I34"/>
     <mergeCell ref="A74:I74"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="C33:I33"/>
@@ -16539,12 +16622,6 @@
     <mergeCell ref="A71:I71"/>
     <mergeCell ref="A72:I72"/>
     <mergeCell ref="A73:I73"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="B36:I36"/>
-    <mergeCell ref="B37:I37"/>
-    <mergeCell ref="B38:I38"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B34:I34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F78" r:id="rId1" xr:uid="{FEEC1FD0-8EC9-4705-A829-A4D4505B3FD7}"/>
@@ -16837,7 +16914,7 @@
       </c>
       <c r="L10" s="246">
         <f>'Journal de bord'!G27</f>
-        <v>0.27083333333333343</v>
+        <v>0.44375000000000009</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -16922,7 +16999,7 @@
       </c>
       <c r="L14" s="249">
         <f>SUM(L9:L13)</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -17206,13 +17283,13 @@
       <c r="U4" s="231" t="s">
         <v>101</v>
       </c>
-      <c r="V4" s="445" t="s">
+      <c r="V4" s="460" t="s">
         <v>102</v>
       </c>
-      <c r="W4" s="446"/>
-      <c r="X4" s="446"/>
-      <c r="Y4" s="446"/>
-      <c r="Z4" s="447"/>
+      <c r="W4" s="461"/>
+      <c r="X4" s="461"/>
+      <c r="Y4" s="461"/>
+      <c r="Z4" s="462"/>
     </row>
     <row r="5" spans="1:114" s="135" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="143" t="s">
@@ -17294,13 +17371,13 @@
       <c r="U6" s="148" t="s">
         <v>106</v>
       </c>
-      <c r="V6" s="448" t="s">
+      <c r="V6" s="463" t="s">
         <v>95</v>
       </c>
-      <c r="W6" s="449"/>
-      <c r="X6" s="449"/>
-      <c r="Y6" s="449"/>
-      <c r="Z6" s="450"/>
+      <c r="W6" s="464"/>
+      <c r="X6" s="464"/>
+      <c r="Y6" s="464"/>
+      <c r="Z6" s="465"/>
       <c r="AA6" s="24"/>
       <c r="AB6" s="24"/>
       <c r="AC6" s="24"/>
@@ -17570,11 +17647,11 @@
       <c r="V8" s="232">
         <v>1</v>
       </c>
-      <c r="W8" s="437" t="str">
+      <c r="W8" s="466" t="str">
         <f>IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="X8" s="438"/>
+      <c r="X8" s="467"/>
       <c r="Y8" s="238"/>
       <c r="Z8" s="239" t="s">
         <v>109</v>
@@ -17582,11 +17659,11 @@
       <c r="AA8" s="232">
         <v>1</v>
       </c>
-      <c r="AB8" s="437" t="str">
+      <c r="AB8" s="466" t="str">
         <f t="shared" ref="AB8" si="36">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="AC8" s="438"/>
+      <c r="AC8" s="467"/>
       <c r="AD8" s="238"/>
       <c r="AE8" s="239" t="s">
         <v>109</v>
@@ -17594,11 +17671,11 @@
       <c r="AF8" s="232">
         <v>1</v>
       </c>
-      <c r="AG8" s="437" t="str">
+      <c r="AG8" s="466" t="str">
         <f t="shared" ref="AG8" si="37">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="AH8" s="438"/>
+      <c r="AH8" s="467"/>
       <c r="AI8" s="238"/>
       <c r="AJ8" s="239" t="s">
         <v>109</v>
@@ -17606,11 +17683,11 @@
       <c r="AK8" s="232">
         <v>1</v>
       </c>
-      <c r="AL8" s="437" t="str">
+      <c r="AL8" s="466" t="str">
         <f t="shared" ref="AL8" si="38">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="AM8" s="438"/>
+      <c r="AM8" s="467"/>
       <c r="AN8" s="238"/>
       <c r="AO8" s="239" t="s">
         <v>109</v>
@@ -17618,11 +17695,11 @@
       <c r="AP8" s="232">
         <v>1</v>
       </c>
-      <c r="AQ8" s="437" t="str">
+      <c r="AQ8" s="466" t="str">
         <f t="shared" ref="AQ8" si="39">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="AR8" s="438"/>
+      <c r="AR8" s="467"/>
       <c r="AS8" s="238"/>
       <c r="AT8" s="239" t="s">
         <v>109</v>
@@ -17630,11 +17707,11 @@
       <c r="AU8" s="232">
         <v>1</v>
       </c>
-      <c r="AV8" s="437" t="str">
+      <c r="AV8" s="466" t="str">
         <f t="shared" ref="AV8" si="40">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="AW8" s="438"/>
+      <c r="AW8" s="467"/>
       <c r="AX8" s="238"/>
       <c r="AY8" s="239" t="s">
         <v>109</v>
@@ -17642,11 +17719,11 @@
       <c r="AZ8" s="232">
         <v>1</v>
       </c>
-      <c r="BA8" s="437" t="str">
+      <c r="BA8" s="466" t="str">
         <f t="shared" ref="BA8" si="41">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="BB8" s="438"/>
+      <c r="BB8" s="467"/>
       <c r="BC8" s="238"/>
       <c r="BD8" s="239" t="s">
         <v>109</v>
@@ -17654,11 +17731,11 @@
       <c r="BE8" s="232">
         <v>1</v>
       </c>
-      <c r="BF8" s="437" t="str">
+      <c r="BF8" s="466" t="str">
         <f t="shared" ref="BF8" si="42">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="BG8" s="438"/>
+      <c r="BG8" s="467"/>
       <c r="BH8" s="238"/>
       <c r="BI8" s="239" t="s">
         <v>109</v>
@@ -17666,11 +17743,11 @@
       <c r="BJ8" s="232">
         <v>1</v>
       </c>
-      <c r="BK8" s="437" t="str">
+      <c r="BK8" s="466" t="str">
         <f t="shared" ref="BK8" si="43">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="BL8" s="438"/>
+      <c r="BL8" s="467"/>
       <c r="BM8" s="238"/>
       <c r="BN8" s="239" t="s">
         <v>109</v>
@@ -17678,11 +17755,11 @@
       <c r="BO8" s="232">
         <v>1</v>
       </c>
-      <c r="BP8" s="437" t="str">
+      <c r="BP8" s="466" t="str">
         <f t="shared" ref="BP8" si="44">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="BQ8" s="438"/>
+      <c r="BQ8" s="467"/>
       <c r="BR8" s="238"/>
       <c r="BS8" s="239" t="s">
         <v>109</v>
@@ -17690,11 +17767,11 @@
       <c r="BT8" s="232">
         <v>1</v>
       </c>
-      <c r="BU8" s="437" t="str">
+      <c r="BU8" s="466" t="str">
         <f t="shared" ref="BU8" si="45">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="BV8" s="438"/>
+      <c r="BV8" s="467"/>
       <c r="BW8" s="238"/>
       <c r="BX8" s="239" t="s">
         <v>109</v>
@@ -17702,11 +17779,11 @@
       <c r="BY8" s="232">
         <v>1</v>
       </c>
-      <c r="BZ8" s="437" t="str">
+      <c r="BZ8" s="466" t="str">
         <f t="shared" ref="BZ8" si="46">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CA8" s="438"/>
+      <c r="CA8" s="467"/>
       <c r="CB8" s="238"/>
       <c r="CC8" s="239" t="s">
         <v>109</v>
@@ -17714,11 +17791,11 @@
       <c r="CD8" s="232">
         <v>1</v>
       </c>
-      <c r="CE8" s="437" t="str">
+      <c r="CE8" s="466" t="str">
         <f t="shared" ref="CE8" si="47">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CF8" s="438"/>
+      <c r="CF8" s="467"/>
       <c r="CG8" s="238"/>
       <c r="CH8" s="239" t="s">
         <v>109</v>
@@ -17726,11 +17803,11 @@
       <c r="CI8" s="232">
         <v>1</v>
       </c>
-      <c r="CJ8" s="437" t="str">
+      <c r="CJ8" s="466" t="str">
         <f t="shared" ref="CJ8" si="48">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CK8" s="438"/>
+      <c r="CK8" s="467"/>
       <c r="CL8" s="238"/>
       <c r="CM8" s="239" t="s">
         <v>109</v>
@@ -17738,11 +17815,11 @@
       <c r="CN8" s="232">
         <v>1</v>
       </c>
-      <c r="CO8" s="437" t="str">
+      <c r="CO8" s="466" t="str">
         <f t="shared" ref="CO8" si="49">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CP8" s="438"/>
+      <c r="CP8" s="467"/>
       <c r="CQ8" s="238"/>
       <c r="CR8" s="239" t="s">
         <v>109</v>
@@ -17750,11 +17827,11 @@
       <c r="CS8" s="232">
         <v>1</v>
       </c>
-      <c r="CT8" s="437" t="str">
+      <c r="CT8" s="466" t="str">
         <f t="shared" ref="CT8" si="50">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CU8" s="438"/>
+      <c r="CU8" s="467"/>
       <c r="CV8" s="238"/>
       <c r="CW8" s="239" t="s">
         <v>109</v>
@@ -17762,11 +17839,11 @@
       <c r="CX8" s="232">
         <v>1</v>
       </c>
-      <c r="CY8" s="437" t="str">
+      <c r="CY8" s="466" t="str">
         <f t="shared" ref="CY8" si="51">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="CZ8" s="438"/>
+      <c r="CZ8" s="467"/>
       <c r="DA8" s="238"/>
       <c r="DB8" s="239" t="s">
         <v>109</v>
@@ -17774,11 +17851,11 @@
       <c r="DC8" s="232">
         <v>1</v>
       </c>
-      <c r="DD8" s="437" t="str">
+      <c r="DD8" s="466" t="str">
         <f t="shared" ref="DD8" si="52">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="DE8" s="438"/>
+      <c r="DE8" s="467"/>
       <c r="DF8" s="238"/>
       <c r="DG8" s="239" t="s">
         <v>109</v>
@@ -17786,11 +17863,11 @@
       <c r="DH8" s="232">
         <v>1</v>
       </c>
-      <c r="DI8" s="437" t="str">
+      <c r="DI8" s="466" t="str">
         <f t="shared" ref="DI8" si="53">IF($V$4="hebdomadaire","sem","jour")</f>
         <v>sem</v>
       </c>
-      <c r="DJ8" s="438"/>
+      <c r="DJ8" s="467"/>
     </row>
     <row r="9" spans="1:114" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="150"/>
@@ -17804,291 +17881,291 @@
       <c r="N9" s="150" t="s">
         <v>110</v>
       </c>
-      <c r="O9" s="459">
+      <c r="O9" s="443">
         <v>1</v>
       </c>
-      <c r="P9" s="460"/>
-      <c r="Q9" s="460"/>
-      <c r="R9" s="460"/>
-      <c r="S9" s="461"/>
-      <c r="T9" s="459">
+      <c r="P9" s="444"/>
+      <c r="Q9" s="444"/>
+      <c r="R9" s="444"/>
+      <c r="S9" s="445"/>
+      <c r="T9" s="443">
         <f>O9+1</f>
         <v>2</v>
       </c>
-      <c r="U9" s="460"/>
-      <c r="V9" s="460"/>
-      <c r="W9" s="460"/>
-      <c r="X9" s="461"/>
-      <c r="Y9" s="459">
+      <c r="U9" s="444"/>
+      <c r="V9" s="444"/>
+      <c r="W9" s="444"/>
+      <c r="X9" s="445"/>
+      <c r="Y9" s="443">
         <f t="shared" ref="Y9" si="54">T9+1</f>
         <v>3</v>
       </c>
-      <c r="Z9" s="460"/>
-      <c r="AA9" s="460"/>
-      <c r="AB9" s="460"/>
-      <c r="AC9" s="461"/>
-      <c r="AD9" s="459">
+      <c r="Z9" s="444"/>
+      <c r="AA9" s="444"/>
+      <c r="AB9" s="444"/>
+      <c r="AC9" s="445"/>
+      <c r="AD9" s="443">
         <f t="shared" ref="AD9" si="55">Y9+1</f>
         <v>4</v>
       </c>
-      <c r="AE9" s="460"/>
-      <c r="AF9" s="460"/>
-      <c r="AG9" s="460"/>
-      <c r="AH9" s="461"/>
-      <c r="AI9" s="459">
+      <c r="AE9" s="444"/>
+      <c r="AF9" s="444"/>
+      <c r="AG9" s="444"/>
+      <c r="AH9" s="445"/>
+      <c r="AI9" s="443">
         <f t="shared" ref="AI9" si="56">AD9+1</f>
         <v>5</v>
       </c>
-      <c r="AJ9" s="460"/>
-      <c r="AK9" s="460"/>
-      <c r="AL9" s="460"/>
-      <c r="AM9" s="461"/>
-      <c r="AN9" s="459">
+      <c r="AJ9" s="444"/>
+      <c r="AK9" s="444"/>
+      <c r="AL9" s="444"/>
+      <c r="AM9" s="445"/>
+      <c r="AN9" s="443">
         <f t="shared" ref="AN9" si="57">AI9+1</f>
         <v>6</v>
       </c>
-      <c r="AO9" s="460"/>
-      <c r="AP9" s="460"/>
-      <c r="AQ9" s="460"/>
-      <c r="AR9" s="461"/>
-      <c r="AS9" s="459">
+      <c r="AO9" s="444"/>
+      <c r="AP9" s="444"/>
+      <c r="AQ9" s="444"/>
+      <c r="AR9" s="445"/>
+      <c r="AS9" s="443">
         <f t="shared" ref="AS9" si="58">AN9+1</f>
         <v>7</v>
       </c>
-      <c r="AT9" s="460"/>
-      <c r="AU9" s="460"/>
-      <c r="AV9" s="460"/>
-      <c r="AW9" s="461"/>
-      <c r="AX9" s="459">
+      <c r="AT9" s="444"/>
+      <c r="AU9" s="444"/>
+      <c r="AV9" s="444"/>
+      <c r="AW9" s="445"/>
+      <c r="AX9" s="443">
         <f t="shared" ref="AX9" si="59">AS9+1</f>
         <v>8</v>
       </c>
-      <c r="AY9" s="460"/>
-      <c r="AZ9" s="460"/>
-      <c r="BA9" s="460"/>
-      <c r="BB9" s="461"/>
-      <c r="BC9" s="459">
+      <c r="AY9" s="444"/>
+      <c r="AZ9" s="444"/>
+      <c r="BA9" s="444"/>
+      <c r="BB9" s="445"/>
+      <c r="BC9" s="443">
         <f t="shared" ref="BC9" si="60">AX9+1</f>
         <v>9</v>
       </c>
-      <c r="BD9" s="460"/>
-      <c r="BE9" s="460"/>
-      <c r="BF9" s="460"/>
-      <c r="BG9" s="461"/>
-      <c r="BH9" s="459">
+      <c r="BD9" s="444"/>
+      <c r="BE9" s="444"/>
+      <c r="BF9" s="444"/>
+      <c r="BG9" s="445"/>
+      <c r="BH9" s="443">
         <f t="shared" ref="BH9" si="61">BC9+1</f>
         <v>10</v>
       </c>
-      <c r="BI9" s="460"/>
-      <c r="BJ9" s="460"/>
-      <c r="BK9" s="460"/>
-      <c r="BL9" s="461"/>
-      <c r="BM9" s="459">
+      <c r="BI9" s="444"/>
+      <c r="BJ9" s="444"/>
+      <c r="BK9" s="444"/>
+      <c r="BL9" s="445"/>
+      <c r="BM9" s="443">
         <f t="shared" ref="BM9" si="62">BH9+1</f>
         <v>11</v>
       </c>
-      <c r="BN9" s="460"/>
-      <c r="BO9" s="460"/>
-      <c r="BP9" s="460"/>
-      <c r="BQ9" s="461"/>
-      <c r="BR9" s="459">
+      <c r="BN9" s="444"/>
+      <c r="BO9" s="444"/>
+      <c r="BP9" s="444"/>
+      <c r="BQ9" s="445"/>
+      <c r="BR9" s="443">
         <f t="shared" ref="BR9" si="63">BM9+1</f>
         <v>12</v>
       </c>
-      <c r="BS9" s="460"/>
-      <c r="BT9" s="460"/>
-      <c r="BU9" s="460"/>
-      <c r="BV9" s="461"/>
-      <c r="BW9" s="459">
+      <c r="BS9" s="444"/>
+      <c r="BT9" s="444"/>
+      <c r="BU9" s="444"/>
+      <c r="BV9" s="445"/>
+      <c r="BW9" s="443">
         <f t="shared" ref="BW9" si="64">BR9+1</f>
         <v>13</v>
       </c>
-      <c r="BX9" s="460"/>
-      <c r="BY9" s="460"/>
-      <c r="BZ9" s="460"/>
-      <c r="CA9" s="461"/>
-      <c r="CB9" s="459">
+      <c r="BX9" s="444"/>
+      <c r="BY9" s="444"/>
+      <c r="BZ9" s="444"/>
+      <c r="CA9" s="445"/>
+      <c r="CB9" s="443">
         <f t="shared" ref="CB9" si="65">BW9+1</f>
         <v>14</v>
       </c>
-      <c r="CC9" s="460"/>
-      <c r="CD9" s="460"/>
-      <c r="CE9" s="460"/>
-      <c r="CF9" s="461"/>
-      <c r="CG9" s="459">
+      <c r="CC9" s="444"/>
+      <c r="CD9" s="444"/>
+      <c r="CE9" s="444"/>
+      <c r="CF9" s="445"/>
+      <c r="CG9" s="443">
         <f t="shared" ref="CG9" si="66">CB9+1</f>
         <v>15</v>
       </c>
-      <c r="CH9" s="460"/>
-      <c r="CI9" s="460"/>
-      <c r="CJ9" s="460"/>
-      <c r="CK9" s="461"/>
-      <c r="CL9" s="459">
+      <c r="CH9" s="444"/>
+      <c r="CI9" s="444"/>
+      <c r="CJ9" s="444"/>
+      <c r="CK9" s="445"/>
+      <c r="CL9" s="443">
         <f t="shared" ref="CL9" si="67">CG9+1</f>
         <v>16</v>
       </c>
-      <c r="CM9" s="460"/>
-      <c r="CN9" s="460"/>
-      <c r="CO9" s="460"/>
-      <c r="CP9" s="461"/>
-      <c r="CQ9" s="459">
+      <c r="CM9" s="444"/>
+      <c r="CN9" s="444"/>
+      <c r="CO9" s="444"/>
+      <c r="CP9" s="445"/>
+      <c r="CQ9" s="443">
         <f t="shared" ref="CQ9" si="68">CL9+1</f>
         <v>17</v>
       </c>
-      <c r="CR9" s="460"/>
-      <c r="CS9" s="460"/>
-      <c r="CT9" s="460"/>
-      <c r="CU9" s="461"/>
-      <c r="CV9" s="459">
+      <c r="CR9" s="444"/>
+      <c r="CS9" s="444"/>
+      <c r="CT9" s="444"/>
+      <c r="CU9" s="445"/>
+      <c r="CV9" s="443">
         <f t="shared" ref="CV9" si="69">CQ9+1</f>
         <v>18</v>
       </c>
-      <c r="CW9" s="460"/>
-      <c r="CX9" s="460"/>
-      <c r="CY9" s="460"/>
-      <c r="CZ9" s="461"/>
-      <c r="DA9" s="459">
+      <c r="CW9" s="444"/>
+      <c r="CX9" s="444"/>
+      <c r="CY9" s="444"/>
+      <c r="CZ9" s="445"/>
+      <c r="DA9" s="443">
         <f t="shared" ref="DA9" si="70">CV9+1</f>
         <v>19</v>
       </c>
-      <c r="DB9" s="460"/>
-      <c r="DC9" s="460"/>
-      <c r="DD9" s="460"/>
-      <c r="DE9" s="461"/>
-      <c r="DF9" s="459">
+      <c r="DB9" s="444"/>
+      <c r="DC9" s="444"/>
+      <c r="DD9" s="444"/>
+      <c r="DE9" s="445"/>
+      <c r="DF9" s="443">
         <f t="shared" ref="DF9" si="71">DA9+1</f>
         <v>20</v>
       </c>
-      <c r="DG9" s="460"/>
-      <c r="DH9" s="460"/>
-      <c r="DI9" s="460"/>
-      <c r="DJ9" s="461"/>
+      <c r="DG9" s="444"/>
+      <c r="DH9" s="444"/>
+      <c r="DI9" s="444"/>
+      <c r="DJ9" s="445"/>
     </row>
     <row r="10" spans="1:114" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="E10" s="456" t="s">
+      <c r="E10" s="457" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="457"/>
-      <c r="G10" s="457"/>
-      <c r="H10" s="457"/>
-      <c r="I10" s="458"/>
+      <c r="F10" s="458"/>
+      <c r="G10" s="458"/>
+      <c r="H10" s="458"/>
+      <c r="I10" s="459"/>
       <c r="M10" s="152"/>
       <c r="N10" s="150" t="s">
         <v>112</v>
       </c>
-      <c r="O10" s="451"/>
-      <c r="P10" s="452"/>
-      <c r="Q10" s="452"/>
-      <c r="R10" s="452"/>
-      <c r="S10" s="453"/>
-      <c r="T10" s="451"/>
-      <c r="U10" s="452"/>
-      <c r="V10" s="452"/>
-      <c r="W10" s="452"/>
-      <c r="X10" s="453"/>
-      <c r="Y10" s="451"/>
-      <c r="Z10" s="452"/>
-      <c r="AA10" s="452"/>
-      <c r="AB10" s="452"/>
-      <c r="AC10" s="453"/>
-      <c r="AD10" s="451"/>
-      <c r="AE10" s="452"/>
-      <c r="AF10" s="452"/>
-      <c r="AG10" s="452"/>
-      <c r="AH10" s="453"/>
-      <c r="AI10" s="451"/>
-      <c r="AJ10" s="452"/>
-      <c r="AK10" s="452"/>
-      <c r="AL10" s="452"/>
-      <c r="AM10" s="453"/>
-      <c r="AN10" s="451"/>
-      <c r="AO10" s="452"/>
-      <c r="AP10" s="452"/>
-      <c r="AQ10" s="452"/>
-      <c r="AR10" s="453"/>
-      <c r="AS10" s="451"/>
-      <c r="AT10" s="452"/>
-      <c r="AU10" s="452"/>
-      <c r="AV10" s="452"/>
-      <c r="AW10" s="453"/>
-      <c r="AX10" s="451"/>
-      <c r="AY10" s="452"/>
-      <c r="AZ10" s="452"/>
-      <c r="BA10" s="452"/>
-      <c r="BB10" s="453"/>
-      <c r="BC10" s="451"/>
-      <c r="BD10" s="452"/>
-      <c r="BE10" s="452"/>
-      <c r="BF10" s="452"/>
-      <c r="BG10" s="453"/>
-      <c r="BH10" s="451"/>
-      <c r="BI10" s="452"/>
-      <c r="BJ10" s="452"/>
-      <c r="BK10" s="452"/>
-      <c r="BL10" s="453"/>
-      <c r="BM10" s="451" t="s">
+      <c r="O10" s="446"/>
+      <c r="P10" s="447"/>
+      <c r="Q10" s="447"/>
+      <c r="R10" s="447"/>
+      <c r="S10" s="448"/>
+      <c r="T10" s="446"/>
+      <c r="U10" s="447"/>
+      <c r="V10" s="447"/>
+      <c r="W10" s="447"/>
+      <c r="X10" s="448"/>
+      <c r="Y10" s="446"/>
+      <c r="Z10" s="447"/>
+      <c r="AA10" s="447"/>
+      <c r="AB10" s="447"/>
+      <c r="AC10" s="448"/>
+      <c r="AD10" s="446"/>
+      <c r="AE10" s="447"/>
+      <c r="AF10" s="447"/>
+      <c r="AG10" s="447"/>
+      <c r="AH10" s="448"/>
+      <c r="AI10" s="446"/>
+      <c r="AJ10" s="447"/>
+      <c r="AK10" s="447"/>
+      <c r="AL10" s="447"/>
+      <c r="AM10" s="448"/>
+      <c r="AN10" s="446"/>
+      <c r="AO10" s="447"/>
+      <c r="AP10" s="447"/>
+      <c r="AQ10" s="447"/>
+      <c r="AR10" s="448"/>
+      <c r="AS10" s="446"/>
+      <c r="AT10" s="447"/>
+      <c r="AU10" s="447"/>
+      <c r="AV10" s="447"/>
+      <c r="AW10" s="448"/>
+      <c r="AX10" s="446"/>
+      <c r="AY10" s="447"/>
+      <c r="AZ10" s="447"/>
+      <c r="BA10" s="447"/>
+      <c r="BB10" s="448"/>
+      <c r="BC10" s="446"/>
+      <c r="BD10" s="447"/>
+      <c r="BE10" s="447"/>
+      <c r="BF10" s="447"/>
+      <c r="BG10" s="448"/>
+      <c r="BH10" s="446"/>
+      <c r="BI10" s="447"/>
+      <c r="BJ10" s="447"/>
+      <c r="BK10" s="447"/>
+      <c r="BL10" s="448"/>
+      <c r="BM10" s="446" t="s">
         <v>113</v>
       </c>
-      <c r="BN10" s="452"/>
-      <c r="BO10" s="452"/>
-      <c r="BP10" s="452"/>
-      <c r="BQ10" s="453"/>
-      <c r="BR10" s="451" t="s">
+      <c r="BN10" s="447"/>
+      <c r="BO10" s="447"/>
+      <c r="BP10" s="447"/>
+      <c r="BQ10" s="448"/>
+      <c r="BR10" s="446" t="s">
         <v>113</v>
       </c>
-      <c r="BS10" s="452"/>
-      <c r="BT10" s="452"/>
-      <c r="BU10" s="452"/>
-      <c r="BV10" s="453"/>
-      <c r="BW10" s="451"/>
-      <c r="BX10" s="452"/>
-      <c r="BY10" s="452"/>
-      <c r="BZ10" s="452"/>
-      <c r="CA10" s="453"/>
-      <c r="CB10" s="451"/>
-      <c r="CC10" s="452"/>
-      <c r="CD10" s="452"/>
-      <c r="CE10" s="452"/>
-      <c r="CF10" s="453"/>
-      <c r="CG10" s="451"/>
-      <c r="CH10" s="452"/>
-      <c r="CI10" s="452"/>
-      <c r="CJ10" s="452"/>
-      <c r="CK10" s="453"/>
-      <c r="CL10" s="451" t="s">
+      <c r="BS10" s="447"/>
+      <c r="BT10" s="447"/>
+      <c r="BU10" s="447"/>
+      <c r="BV10" s="448"/>
+      <c r="BW10" s="446"/>
+      <c r="BX10" s="447"/>
+      <c r="BY10" s="447"/>
+      <c r="BZ10" s="447"/>
+      <c r="CA10" s="448"/>
+      <c r="CB10" s="446"/>
+      <c r="CC10" s="447"/>
+      <c r="CD10" s="447"/>
+      <c r="CE10" s="447"/>
+      <c r="CF10" s="448"/>
+      <c r="CG10" s="446"/>
+      <c r="CH10" s="447"/>
+      <c r="CI10" s="447"/>
+      <c r="CJ10" s="447"/>
+      <c r="CK10" s="448"/>
+      <c r="CL10" s="446" t="s">
         <v>114</v>
       </c>
-      <c r="CM10" s="452"/>
-      <c r="CN10" s="452"/>
-      <c r="CO10" s="452"/>
-      <c r="CP10" s="453"/>
-      <c r="CQ10" s="451"/>
-      <c r="CR10" s="452"/>
-      <c r="CS10" s="452"/>
-      <c r="CT10" s="452"/>
-      <c r="CU10" s="453"/>
-      <c r="CV10" s="451" t="s">
+      <c r="CM10" s="447"/>
+      <c r="CN10" s="447"/>
+      <c r="CO10" s="447"/>
+      <c r="CP10" s="448"/>
+      <c r="CQ10" s="446"/>
+      <c r="CR10" s="447"/>
+      <c r="CS10" s="447"/>
+      <c r="CT10" s="447"/>
+      <c r="CU10" s="448"/>
+      <c r="CV10" s="446" t="s">
         <v>115</v>
       </c>
-      <c r="CW10" s="452"/>
-      <c r="CX10" s="452"/>
-      <c r="CY10" s="452"/>
-      <c r="CZ10" s="453"/>
-      <c r="DA10" s="451"/>
-      <c r="DB10" s="452"/>
-      <c r="DC10" s="452"/>
-      <c r="DD10" s="452"/>
-      <c r="DE10" s="453"/>
-      <c r="DF10" s="451" t="s">
+      <c r="CW10" s="447"/>
+      <c r="CX10" s="447"/>
+      <c r="CY10" s="447"/>
+      <c r="CZ10" s="448"/>
+      <c r="DA10" s="446"/>
+      <c r="DB10" s="447"/>
+      <c r="DC10" s="447"/>
+      <c r="DD10" s="447"/>
+      <c r="DE10" s="448"/>
+      <c r="DF10" s="446" t="s">
         <v>116</v>
       </c>
-      <c r="DG10" s="452"/>
-      <c r="DH10" s="452"/>
-      <c r="DI10" s="452"/>
-      <c r="DJ10" s="453"/>
+      <c r="DG10" s="447"/>
+      <c r="DH10" s="447"/>
+      <c r="DI10" s="447"/>
+      <c r="DJ10" s="448"/>
     </row>
     <row r="11" spans="1:114" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="454" t="s">
+      <c r="A11" s="455" t="s">
         <v>117</v>
       </c>
       <c r="B11" s="153" t="s">
@@ -18131,409 +18208,409 @@
         <v>95</v>
       </c>
       <c r="N11" s="164"/>
-      <c r="O11" s="443">
+      <c r="O11" s="453">
         <f>IF($V5=45,"P1",IF($V5=60,"H1",O7))</f>
         <v>46279</v>
       </c>
-      <c r="P11" s="439">
+      <c r="P11" s="449">
         <f>IF($V5=45,"P2",IF($V5=60,"H2",O7+1))</f>
         <v>46280</v>
       </c>
-      <c r="Q11" s="439">
+      <c r="Q11" s="449">
         <f>IF($V5=45,"P3",IF($V5=60,"H3",O7+2))</f>
         <v>46281</v>
       </c>
-      <c r="R11" s="439">
+      <c r="R11" s="449">
         <f>IF($V5=45,"P4",IF($V5=60,"H4",O7+3))</f>
         <v>46282</v>
       </c>
-      <c r="S11" s="441">
+      <c r="S11" s="451">
         <f>IF($V5=45,"P5",IF($V5=60,"H5",O7+4))</f>
         <v>46283</v>
       </c>
-      <c r="T11" s="443">
+      <c r="T11" s="453">
         <f t="shared" ref="T11" si="72">IF($V5=45,"P1",IF($V5=60,"H1",T7))</f>
         <v>46286</v>
       </c>
-      <c r="U11" s="439">
+      <c r="U11" s="449">
         <f t="shared" ref="U11" si="73">IF($V5=45,"P2",IF($V5=60,"H2",T7+1))</f>
         <v>46287</v>
       </c>
-      <c r="V11" s="439">
+      <c r="V11" s="449">
         <f t="shared" ref="V11" si="74">IF($V5=45,"P3",IF($V5=60,"H3",T7+2))</f>
         <v>46288</v>
       </c>
-      <c r="W11" s="439">
+      <c r="W11" s="449">
         <f t="shared" ref="W11" si="75">IF($V5=45,"P4",IF($V5=60,"H4",T7+3))</f>
         <v>46289</v>
       </c>
-      <c r="X11" s="441">
+      <c r="X11" s="451">
         <f t="shared" ref="X11" si="76">IF($V5=45,"P5",IF($V5=60,"H5",T7+4))</f>
         <v>46290</v>
       </c>
-      <c r="Y11" s="443">
+      <c r="Y11" s="453">
         <f t="shared" ref="Y11" si="77">IF($V5=45,"P1",IF($V5=60,"H1",Y7))</f>
         <v>46293</v>
       </c>
-      <c r="Z11" s="439">
+      <c r="Z11" s="449">
         <f t="shared" ref="Z11" si="78">IF($V5=45,"P2",IF($V5=60,"H2",Y7+1))</f>
         <v>46294</v>
       </c>
-      <c r="AA11" s="439">
+      <c r="AA11" s="449">
         <f t="shared" ref="AA11" si="79">IF($V5=45,"P3",IF($V5=60,"H3",Y7+2))</f>
         <v>46295</v>
       </c>
-      <c r="AB11" s="439">
+      <c r="AB11" s="449">
         <f t="shared" ref="AB11" si="80">IF($V5=45,"P4",IF($V5=60,"H4",Y7+3))</f>
         <v>46296</v>
       </c>
-      <c r="AC11" s="441">
+      <c r="AC11" s="451">
         <f t="shared" ref="AC11" si="81">IF($V5=45,"P5",IF($V5=60,"H5",Y7+4))</f>
         <v>46297</v>
       </c>
-      <c r="AD11" s="443">
+      <c r="AD11" s="453">
         <f t="shared" ref="AD11" si="82">IF($V5=45,"P1",IF($V5=60,"H1",AD7))</f>
         <v>46300</v>
       </c>
-      <c r="AE11" s="439">
+      <c r="AE11" s="449">
         <f t="shared" ref="AE11" si="83">IF($V5=45,"P2",IF($V5=60,"H2",AD7+1))</f>
         <v>46301</v>
       </c>
-      <c r="AF11" s="439">
+      <c r="AF11" s="449">
         <f t="shared" ref="AF11" si="84">IF($V5=45,"P3",IF($V5=60,"H3",AD7+2))</f>
         <v>46302</v>
       </c>
-      <c r="AG11" s="439">
+      <c r="AG11" s="449">
         <f t="shared" ref="AG11" si="85">IF($V5=45,"P4",IF($V5=60,"H4",AD7+3))</f>
         <v>46303</v>
       </c>
-      <c r="AH11" s="441">
+      <c r="AH11" s="451">
         <f t="shared" ref="AH11" si="86">IF($V5=45,"P5",IF($V5=60,"H5",AD7+4))</f>
         <v>46304</v>
       </c>
-      <c r="AI11" s="443">
+      <c r="AI11" s="453">
         <f t="shared" ref="AI11" si="87">IF($V5=45,"P1",IF($V5=60,"H1",AI7))</f>
         <v>46307</v>
       </c>
-      <c r="AJ11" s="439">
+      <c r="AJ11" s="449">
         <f t="shared" ref="AJ11" si="88">IF($V5=45,"P2",IF($V5=60,"H2",AI7+1))</f>
         <v>46308</v>
       </c>
-      <c r="AK11" s="439">
+      <c r="AK11" s="449">
         <f t="shared" ref="AK11" si="89">IF($V5=45,"P3",IF($V5=60,"H3",AI7+2))</f>
         <v>46309</v>
       </c>
-      <c r="AL11" s="439">
+      <c r="AL11" s="449">
         <f t="shared" ref="AL11" si="90">IF($V5=45,"P4",IF($V5=60,"H4",AI7+3))</f>
         <v>46310</v>
       </c>
-      <c r="AM11" s="441">
+      <c r="AM11" s="451">
         <f t="shared" ref="AM11" si="91">IF($V5=45,"P5",IF($V5=60,"H5",AI7+4))</f>
         <v>46311</v>
       </c>
-      <c r="AN11" s="443">
+      <c r="AN11" s="453">
         <f t="shared" ref="AN11" si="92">IF($V5=45,"P1",IF($V5=60,"H1",AN7))</f>
         <v>46314</v>
       </c>
-      <c r="AO11" s="439">
+      <c r="AO11" s="449">
         <f t="shared" ref="AO11" si="93">IF($V5=45,"P2",IF($V5=60,"H2",AN7+1))</f>
         <v>46315</v>
       </c>
-      <c r="AP11" s="439">
+      <c r="AP11" s="449">
         <f t="shared" ref="AP11" si="94">IF($V5=45,"P3",IF($V5=60,"H3",AN7+2))</f>
         <v>46316</v>
       </c>
-      <c r="AQ11" s="439">
+      <c r="AQ11" s="449">
         <f t="shared" ref="AQ11" si="95">IF($V5=45,"P4",IF($V5=60,"H4",AN7+3))</f>
         <v>46317</v>
       </c>
-      <c r="AR11" s="441">
+      <c r="AR11" s="451">
         <f t="shared" ref="AR11" si="96">IF($V5=45,"P5",IF($V5=60,"H5",AN7+4))</f>
         <v>46318</v>
       </c>
-      <c r="AS11" s="443">
+      <c r="AS11" s="453">
         <f t="shared" ref="AS11" si="97">IF($V5=45,"P1",IF($V5=60,"H1",AS7))</f>
         <v>46321</v>
       </c>
-      <c r="AT11" s="439">
+      <c r="AT11" s="449">
         <f t="shared" ref="AT11" si="98">IF($V5=45,"P2",IF($V5=60,"H2",AS7+1))</f>
         <v>46322</v>
       </c>
-      <c r="AU11" s="439">
+      <c r="AU11" s="449">
         <f t="shared" ref="AU11" si="99">IF($V5=45,"P3",IF($V5=60,"H3",AS7+2))</f>
         <v>46323</v>
       </c>
-      <c r="AV11" s="439">
+      <c r="AV11" s="449">
         <f t="shared" ref="AV11" si="100">IF($V5=45,"P4",IF($V5=60,"H4",AS7+3))</f>
         <v>46324</v>
       </c>
-      <c r="AW11" s="441">
+      <c r="AW11" s="451">
         <f t="shared" ref="AW11" si="101">IF($V5=45,"P5",IF($V5=60,"H5",AS7+4))</f>
         <v>46325</v>
       </c>
-      <c r="AX11" s="443">
+      <c r="AX11" s="453">
         <f t="shared" ref="AX11" si="102">IF($V5=45,"P1",IF($V5=60,"H1",AX7))</f>
         <v>46328</v>
       </c>
-      <c r="AY11" s="439">
+      <c r="AY11" s="449">
         <f t="shared" ref="AY11" si="103">IF($V5=45,"P2",IF($V5=60,"H2",AX7+1))</f>
         <v>46329</v>
       </c>
-      <c r="AZ11" s="439">
+      <c r="AZ11" s="449">
         <f t="shared" ref="AZ11" si="104">IF($V5=45,"P3",IF($V5=60,"H3",AX7+2))</f>
         <v>46330</v>
       </c>
-      <c r="BA11" s="439">
+      <c r="BA11" s="449">
         <f t="shared" ref="BA11" si="105">IF($V5=45,"P4",IF($V5=60,"H4",AX7+3))</f>
         <v>46331</v>
       </c>
-      <c r="BB11" s="441">
+      <c r="BB11" s="451">
         <f t="shared" ref="BB11" si="106">IF($V5=45,"P5",IF($V5=60,"H5",AX7+4))</f>
         <v>46332</v>
       </c>
-      <c r="BC11" s="443">
+      <c r="BC11" s="453">
         <f t="shared" ref="BC11" si="107">IF($V5=45,"P1",IF($V5=60,"H1",BC7))</f>
         <v>46335</v>
       </c>
-      <c r="BD11" s="439">
+      <c r="BD11" s="449">
         <f t="shared" ref="BD11" si="108">IF($V5=45,"P2",IF($V5=60,"H2",BC7+1))</f>
         <v>46336</v>
       </c>
-      <c r="BE11" s="439">
+      <c r="BE11" s="449">
         <f t="shared" ref="BE11" si="109">IF($V5=45,"P3",IF($V5=60,"H3",BC7+2))</f>
         <v>46337</v>
       </c>
-      <c r="BF11" s="439">
+      <c r="BF11" s="449">
         <f t="shared" ref="BF11" si="110">IF($V5=45,"P4",IF($V5=60,"H4",BC7+3))</f>
         <v>46338</v>
       </c>
-      <c r="BG11" s="441">
+      <c r="BG11" s="451">
         <f t="shared" ref="BG11" si="111">IF($V5=45,"P5",IF($V5=60,"H5",BC7+4))</f>
         <v>46339</v>
       </c>
-      <c r="BH11" s="443">
+      <c r="BH11" s="453">
         <f t="shared" ref="BH11" si="112">IF($V5=45,"P1",IF($V5=60,"H1",BH7))</f>
         <v>46342</v>
       </c>
-      <c r="BI11" s="439">
+      <c r="BI11" s="449">
         <f t="shared" ref="BI11" si="113">IF($V5=45,"P2",IF($V5=60,"H2",BH7+1))</f>
         <v>46343</v>
       </c>
-      <c r="BJ11" s="439">
+      <c r="BJ11" s="449">
         <f t="shared" ref="BJ11" si="114">IF($V5=45,"P3",IF($V5=60,"H3",BH7+2))</f>
         <v>46344</v>
       </c>
-      <c r="BK11" s="439">
+      <c r="BK11" s="449">
         <f t="shared" ref="BK11" si="115">IF($V5=45,"P4",IF($V5=60,"H4",BH7+3))</f>
         <v>46345</v>
       </c>
-      <c r="BL11" s="441">
+      <c r="BL11" s="451">
         <f t="shared" ref="BL11" si="116">IF($V5=45,"P5",IF($V5=60,"H5",BH7+4))</f>
         <v>46346</v>
       </c>
-      <c r="BM11" s="443">
+      <c r="BM11" s="453">
         <f t="shared" ref="BM11" si="117">IF($V5=45,"P1",IF($V5=60,"H1",BM7))</f>
         <v>46349</v>
       </c>
-      <c r="BN11" s="439">
+      <c r="BN11" s="449">
         <f t="shared" ref="BN11" si="118">IF($V5=45,"P2",IF($V5=60,"H2",BM7+1))</f>
         <v>46350</v>
       </c>
-      <c r="BO11" s="439">
+      <c r="BO11" s="449">
         <f t="shared" ref="BO11" si="119">IF($V5=45,"P3",IF($V5=60,"H3",BM7+2))</f>
         <v>46351</v>
       </c>
-      <c r="BP11" s="439">
+      <c r="BP11" s="449">
         <f t="shared" ref="BP11" si="120">IF($V5=45,"P4",IF($V5=60,"H4",BM7+3))</f>
         <v>46352</v>
       </c>
-      <c r="BQ11" s="441">
+      <c r="BQ11" s="451">
         <f t="shared" ref="BQ11" si="121">IF($V5=45,"P5",IF($V5=60,"H5",BM7+4))</f>
         <v>46353</v>
       </c>
-      <c r="BR11" s="443">
+      <c r="BR11" s="453">
         <f t="shared" ref="BR11" si="122">IF($V5=45,"P1",IF($V5=60,"H1",BR7))</f>
         <v>46356</v>
       </c>
-      <c r="BS11" s="439">
+      <c r="BS11" s="449">
         <f t="shared" ref="BS11" si="123">IF($V5=45,"P2",IF($V5=60,"H2",BR7+1))</f>
         <v>46357</v>
       </c>
-      <c r="BT11" s="439">
+      <c r="BT11" s="449">
         <f t="shared" ref="BT11" si="124">IF($V5=45,"P3",IF($V5=60,"H3",BR7+2))</f>
         <v>46358</v>
       </c>
-      <c r="BU11" s="439">
+      <c r="BU11" s="449">
         <f t="shared" ref="BU11" si="125">IF($V5=45,"P4",IF($V5=60,"H4",BR7+3))</f>
         <v>46359</v>
       </c>
-      <c r="BV11" s="441">
+      <c r="BV11" s="451">
         <f t="shared" ref="BV11" si="126">IF($V5=45,"P5",IF($V5=60,"H5",BR7+4))</f>
         <v>46360</v>
       </c>
-      <c r="BW11" s="443">
+      <c r="BW11" s="453">
         <f t="shared" ref="BW11" si="127">IF($V5=45,"P1",IF($V5=60,"H1",BW7))</f>
         <v>46363</v>
       </c>
-      <c r="BX11" s="439">
+      <c r="BX11" s="449">
         <f t="shared" ref="BX11" si="128">IF($V5=45,"P2",IF($V5=60,"H2",BW7+1))</f>
         <v>46364</v>
       </c>
-      <c r="BY11" s="439">
+      <c r="BY11" s="449">
         <f t="shared" ref="BY11" si="129">IF($V5=45,"P3",IF($V5=60,"H3",BW7+2))</f>
         <v>46365</v>
       </c>
-      <c r="BZ11" s="439">
+      <c r="BZ11" s="449">
         <f t="shared" ref="BZ11" si="130">IF($V5=45,"P4",IF($V5=60,"H4",BW7+3))</f>
         <v>46366</v>
       </c>
-      <c r="CA11" s="441">
+      <c r="CA11" s="451">
         <f t="shared" ref="CA11" si="131">IF($V5=45,"P5",IF($V5=60,"H5",BW7+4))</f>
         <v>46367</v>
       </c>
-      <c r="CB11" s="443">
+      <c r="CB11" s="453">
         <f t="shared" ref="CB11" si="132">IF($V5=45,"P1",IF($V5=60,"H1",CB7))</f>
         <v>46370</v>
       </c>
-      <c r="CC11" s="439">
+      <c r="CC11" s="449">
         <f t="shared" ref="CC11" si="133">IF($V5=45,"P2",IF($V5=60,"H2",CB7+1))</f>
         <v>46371</v>
       </c>
-      <c r="CD11" s="439">
+      <c r="CD11" s="449">
         <f t="shared" ref="CD11" si="134">IF($V5=45,"P3",IF($V5=60,"H3",CB7+2))</f>
         <v>46372</v>
       </c>
-      <c r="CE11" s="439">
+      <c r="CE11" s="449">
         <f t="shared" ref="CE11" si="135">IF($V5=45,"P4",IF($V5=60,"H4",CB7+3))</f>
         <v>46373</v>
       </c>
-      <c r="CF11" s="441">
+      <c r="CF11" s="451">
         <f t="shared" ref="CF11" si="136">IF($V5=45,"P5",IF($V5=60,"H5",CB7+4))</f>
         <v>46374</v>
       </c>
-      <c r="CG11" s="443">
+      <c r="CG11" s="453">
         <f t="shared" ref="CG11" si="137">IF($V5=45,"P1",IF($V5=60,"H1",CG7))</f>
         <v>46377</v>
       </c>
-      <c r="CH11" s="439">
+      <c r="CH11" s="449">
         <f t="shared" ref="CH11" si="138">IF($V5=45,"P2",IF($V5=60,"H2",CG7+1))</f>
         <v>46378</v>
       </c>
-      <c r="CI11" s="439">
+      <c r="CI11" s="449">
         <f t="shared" ref="CI11" si="139">IF($V5=45,"P3",IF($V5=60,"H3",CG7+2))</f>
         <v>46379</v>
       </c>
-      <c r="CJ11" s="439">
+      <c r="CJ11" s="449">
         <f t="shared" ref="CJ11" si="140">IF($V5=45,"P4",IF($V5=60,"H4",CG7+3))</f>
         <v>46380</v>
       </c>
-      <c r="CK11" s="441">
+      <c r="CK11" s="451">
         <f t="shared" ref="CK11" si="141">IF($V5=45,"P5",IF($V5=60,"H5",CG7+4))</f>
         <v>46381</v>
       </c>
-      <c r="CL11" s="443">
+      <c r="CL11" s="453">
         <f t="shared" ref="CL11" si="142">IF($V5=45,"P1",IF($V5=60,"H1",CL7))</f>
         <v>46384</v>
       </c>
-      <c r="CM11" s="439">
+      <c r="CM11" s="449">
         <f t="shared" ref="CM11" si="143">IF($V5=45,"P2",IF($V5=60,"H2",CL7+1))</f>
         <v>46385</v>
       </c>
-      <c r="CN11" s="439">
+      <c r="CN11" s="449">
         <f t="shared" ref="CN11" si="144">IF($V5=45,"P3",IF($V5=60,"H3",CL7+2))</f>
         <v>46386</v>
       </c>
-      <c r="CO11" s="439">
+      <c r="CO11" s="449">
         <f t="shared" ref="CO11" si="145">IF($V5=45,"P4",IF($V5=60,"H4",CL7+3))</f>
         <v>46387</v>
       </c>
-      <c r="CP11" s="441">
+      <c r="CP11" s="451">
         <f t="shared" ref="CP11" si="146">IF($V5=45,"P5",IF($V5=60,"H5",CL7+4))</f>
         <v>46388</v>
       </c>
-      <c r="CQ11" s="443">
+      <c r="CQ11" s="453">
         <f t="shared" ref="CQ11" si="147">IF($V5=45,"P1",IF($V5=60,"H1",CQ7))</f>
         <v>46391</v>
       </c>
-      <c r="CR11" s="439">
+      <c r="CR11" s="449">
         <f t="shared" ref="CR11" si="148">IF($V5=45,"P2",IF($V5=60,"H2",CQ7+1))</f>
         <v>46392</v>
       </c>
-      <c r="CS11" s="439">
+      <c r="CS11" s="449">
         <f t="shared" ref="CS11" si="149">IF($V5=45,"P3",IF($V5=60,"H3",CQ7+2))</f>
         <v>46393</v>
       </c>
-      <c r="CT11" s="439">
+      <c r="CT11" s="449">
         <f t="shared" ref="CT11" si="150">IF($V5=45,"P4",IF($V5=60,"H4",CQ7+3))</f>
         <v>46394</v>
       </c>
-      <c r="CU11" s="441">
+      <c r="CU11" s="451">
         <f t="shared" ref="CU11" si="151">IF($V5=45,"P5",IF($V5=60,"H5",CQ7+4))</f>
         <v>46395</v>
       </c>
-      <c r="CV11" s="443">
+      <c r="CV11" s="453">
         <f t="shared" ref="CV11" si="152">IF($V5=45,"P1",IF($V5=60,"H1",CV7))</f>
         <v>46398</v>
       </c>
-      <c r="CW11" s="439">
+      <c r="CW11" s="449">
         <f t="shared" ref="CW11" si="153">IF($V5=45,"P2",IF($V5=60,"H2",CV7+1))</f>
         <v>46399</v>
       </c>
-      <c r="CX11" s="439">
+      <c r="CX11" s="449">
         <f t="shared" ref="CX11" si="154">IF($V5=45,"P3",IF($V5=60,"H3",CV7+2))</f>
         <v>46400</v>
       </c>
-      <c r="CY11" s="439">
+      <c r="CY11" s="449">
         <f t="shared" ref="CY11" si="155">IF($V5=45,"P4",IF($V5=60,"H4",CV7+3))</f>
         <v>46401</v>
       </c>
-      <c r="CZ11" s="441">
+      <c r="CZ11" s="451">
         <f t="shared" ref="CZ11" si="156">IF($V5=45,"P5",IF($V5=60,"H5",CV7+4))</f>
         <v>46402</v>
       </c>
-      <c r="DA11" s="443">
+      <c r="DA11" s="453">
         <f t="shared" ref="DA11" si="157">IF($V5=45,"P1",IF($V5=60,"H1",DA7))</f>
         <v>46405</v>
       </c>
-      <c r="DB11" s="439">
+      <c r="DB11" s="449">
         <f t="shared" ref="DB11" si="158">IF($V5=45,"P2",IF($V5=60,"H2",DA7+1))</f>
         <v>46406</v>
       </c>
-      <c r="DC11" s="439">
+      <c r="DC11" s="449">
         <f t="shared" ref="DC11" si="159">IF($V5=45,"P3",IF($V5=60,"H3",DA7+2))</f>
         <v>46407</v>
       </c>
-      <c r="DD11" s="439">
+      <c r="DD11" s="449">
         <f t="shared" ref="DD11" si="160">IF($V5=45,"P4",IF($V5=60,"H4",DA7+3))</f>
         <v>46408</v>
       </c>
-      <c r="DE11" s="441">
+      <c r="DE11" s="451">
         <f t="shared" ref="DE11" si="161">IF($V5=45,"P5",IF($V5=60,"H5",DA7+4))</f>
         <v>46409</v>
       </c>
-      <c r="DF11" s="443">
+      <c r="DF11" s="453">
         <f t="shared" ref="DF11" si="162">IF($V5=45,"P1",IF($V5=60,"H1",DF7))</f>
         <v>46412</v>
       </c>
-      <c r="DG11" s="439">
+      <c r="DG11" s="449">
         <f t="shared" ref="DG11" si="163">IF($V5=45,"P2",IF($V5=60,"H2",DF7+1))</f>
         <v>46413</v>
       </c>
-      <c r="DH11" s="439">
+      <c r="DH11" s="449">
         <f t="shared" ref="DH11" si="164">IF($V5=45,"P3",IF($V5=60,"H3",DF7+2))</f>
         <v>46414</v>
       </c>
-      <c r="DI11" s="439">
+      <c r="DI11" s="449">
         <f t="shared" ref="DI11" si="165">IF($V5=45,"P4",IF($V5=60,"H4",DF7+3))</f>
         <v>46415</v>
       </c>
-      <c r="DJ11" s="441">
+      <c r="DJ11" s="451">
         <f t="shared" ref="DJ11" si="166">IF($V5=45,"P5",IF($V5=60,"H5",DF7+4))</f>
         <v>46416</v>
       </c>
     </row>
     <row r="12" spans="1:114" ht="14" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="455"/>
+      <c r="A12" s="456"/>
       <c r="B12" s="165"/>
       <c r="C12" s="166" t="s">
         <v>121</v>
@@ -18574,106 +18651,106 @@
         <v>126</v>
       </c>
       <c r="N12" s="171"/>
-      <c r="O12" s="444"/>
-      <c r="P12" s="440"/>
-      <c r="Q12" s="440"/>
-      <c r="R12" s="440"/>
-      <c r="S12" s="442"/>
-      <c r="T12" s="444"/>
-      <c r="U12" s="440"/>
-      <c r="V12" s="440"/>
-      <c r="W12" s="440"/>
-      <c r="X12" s="442"/>
-      <c r="Y12" s="444"/>
-      <c r="Z12" s="440"/>
-      <c r="AA12" s="440"/>
-      <c r="AB12" s="440"/>
-      <c r="AC12" s="442"/>
-      <c r="AD12" s="444"/>
-      <c r="AE12" s="440"/>
-      <c r="AF12" s="440"/>
-      <c r="AG12" s="440"/>
-      <c r="AH12" s="442"/>
-      <c r="AI12" s="444"/>
-      <c r="AJ12" s="440"/>
-      <c r="AK12" s="440"/>
-      <c r="AL12" s="440"/>
-      <c r="AM12" s="442"/>
-      <c r="AN12" s="444"/>
-      <c r="AO12" s="440"/>
-      <c r="AP12" s="440"/>
-      <c r="AQ12" s="440"/>
-      <c r="AR12" s="442"/>
-      <c r="AS12" s="444"/>
-      <c r="AT12" s="440"/>
-      <c r="AU12" s="440"/>
-      <c r="AV12" s="440"/>
-      <c r="AW12" s="442"/>
-      <c r="AX12" s="444"/>
-      <c r="AY12" s="440"/>
-      <c r="AZ12" s="440"/>
-      <c r="BA12" s="440"/>
-      <c r="BB12" s="442"/>
-      <c r="BC12" s="444"/>
-      <c r="BD12" s="440"/>
-      <c r="BE12" s="440"/>
-      <c r="BF12" s="440"/>
-      <c r="BG12" s="442"/>
-      <c r="BH12" s="444"/>
-      <c r="BI12" s="440"/>
-      <c r="BJ12" s="440"/>
-      <c r="BK12" s="440"/>
-      <c r="BL12" s="442"/>
-      <c r="BM12" s="444"/>
-      <c r="BN12" s="440"/>
-      <c r="BO12" s="440"/>
-      <c r="BP12" s="440"/>
-      <c r="BQ12" s="442"/>
-      <c r="BR12" s="444"/>
-      <c r="BS12" s="440"/>
-      <c r="BT12" s="440"/>
-      <c r="BU12" s="440"/>
-      <c r="BV12" s="442"/>
-      <c r="BW12" s="444"/>
-      <c r="BX12" s="440"/>
-      <c r="BY12" s="440"/>
-      <c r="BZ12" s="440"/>
-      <c r="CA12" s="442"/>
-      <c r="CB12" s="444"/>
-      <c r="CC12" s="440"/>
-      <c r="CD12" s="440"/>
-      <c r="CE12" s="440"/>
-      <c r="CF12" s="442"/>
-      <c r="CG12" s="444"/>
-      <c r="CH12" s="440"/>
-      <c r="CI12" s="440"/>
-      <c r="CJ12" s="440"/>
-      <c r="CK12" s="442"/>
-      <c r="CL12" s="444"/>
-      <c r="CM12" s="440"/>
-      <c r="CN12" s="440"/>
-      <c r="CO12" s="440"/>
-      <c r="CP12" s="442"/>
-      <c r="CQ12" s="444"/>
-      <c r="CR12" s="440"/>
-      <c r="CS12" s="440"/>
-      <c r="CT12" s="440"/>
-      <c r="CU12" s="442"/>
-      <c r="CV12" s="444"/>
-      <c r="CW12" s="440"/>
-      <c r="CX12" s="440"/>
-      <c r="CY12" s="440"/>
-      <c r="CZ12" s="442"/>
-      <c r="DA12" s="444"/>
-      <c r="DB12" s="440"/>
-      <c r="DC12" s="440"/>
-      <c r="DD12" s="440"/>
-      <c r="DE12" s="442"/>
-      <c r="DF12" s="444"/>
-      <c r="DG12" s="440"/>
-      <c r="DH12" s="440"/>
-      <c r="DI12" s="440"/>
-      <c r="DJ12" s="442"/>
+      <c r="O12" s="454"/>
+      <c r="P12" s="450"/>
+      <c r="Q12" s="450"/>
+      <c r="R12" s="450"/>
+      <c r="S12" s="452"/>
+      <c r="T12" s="454"/>
+      <c r="U12" s="450"/>
+      <c r="V12" s="450"/>
+      <c r="W12" s="450"/>
+      <c r="X12" s="452"/>
+      <c r="Y12" s="454"/>
+      <c r="Z12" s="450"/>
+      <c r="AA12" s="450"/>
+      <c r="AB12" s="450"/>
+      <c r="AC12" s="452"/>
+      <c r="AD12" s="454"/>
+      <c r="AE12" s="450"/>
+      <c r="AF12" s="450"/>
+      <c r="AG12" s="450"/>
+      <c r="AH12" s="452"/>
+      <c r="AI12" s="454"/>
+      <c r="AJ12" s="450"/>
+      <c r="AK12" s="450"/>
+      <c r="AL12" s="450"/>
+      <c r="AM12" s="452"/>
+      <c r="AN12" s="454"/>
+      <c r="AO12" s="450"/>
+      <c r="AP12" s="450"/>
+      <c r="AQ12" s="450"/>
+      <c r="AR12" s="452"/>
+      <c r="AS12" s="454"/>
+      <c r="AT12" s="450"/>
+      <c r="AU12" s="450"/>
+      <c r="AV12" s="450"/>
+      <c r="AW12" s="452"/>
+      <c r="AX12" s="454"/>
+      <c r="AY12" s="450"/>
+      <c r="AZ12" s="450"/>
+      <c r="BA12" s="450"/>
+      <c r="BB12" s="452"/>
+      <c r="BC12" s="454"/>
+      <c r="BD12" s="450"/>
+      <c r="BE12" s="450"/>
+      <c r="BF12" s="450"/>
+      <c r="BG12" s="452"/>
+      <c r="BH12" s="454"/>
+      <c r="BI12" s="450"/>
+      <c r="BJ12" s="450"/>
+      <c r="BK12" s="450"/>
+      <c r="BL12" s="452"/>
+      <c r="BM12" s="454"/>
+      <c r="BN12" s="450"/>
+      <c r="BO12" s="450"/>
+      <c r="BP12" s="450"/>
+      <c r="BQ12" s="452"/>
+      <c r="BR12" s="454"/>
+      <c r="BS12" s="450"/>
+      <c r="BT12" s="450"/>
+      <c r="BU12" s="450"/>
+      <c r="BV12" s="452"/>
+      <c r="BW12" s="454"/>
+      <c r="BX12" s="450"/>
+      <c r="BY12" s="450"/>
+      <c r="BZ12" s="450"/>
+      <c r="CA12" s="452"/>
+      <c r="CB12" s="454"/>
+      <c r="CC12" s="450"/>
+      <c r="CD12" s="450"/>
+      <c r="CE12" s="450"/>
+      <c r="CF12" s="452"/>
+      <c r="CG12" s="454"/>
+      <c r="CH12" s="450"/>
+      <c r="CI12" s="450"/>
+      <c r="CJ12" s="450"/>
+      <c r="CK12" s="452"/>
+      <c r="CL12" s="454"/>
+      <c r="CM12" s="450"/>
+      <c r="CN12" s="450"/>
+      <c r="CO12" s="450"/>
+      <c r="CP12" s="452"/>
+      <c r="CQ12" s="454"/>
+      <c r="CR12" s="450"/>
+      <c r="CS12" s="450"/>
+      <c r="CT12" s="450"/>
+      <c r="CU12" s="452"/>
+      <c r="CV12" s="454"/>
+      <c r="CW12" s="450"/>
+      <c r="CX12" s="450"/>
+      <c r="CY12" s="450"/>
+      <c r="CZ12" s="452"/>
+      <c r="DA12" s="454"/>
+      <c r="DB12" s="450"/>
+      <c r="DC12" s="450"/>
+      <c r="DD12" s="450"/>
+      <c r="DE12" s="452"/>
+      <c r="DF12" s="454"/>
+      <c r="DG12" s="450"/>
+      <c r="DH12" s="450"/>
+      <c r="DI12" s="450"/>
+      <c r="DJ12" s="452"/>
     </row>
     <row r="13" spans="1:114" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="345" t="s">
@@ -22834,14 +22911,14 @@
         <v>1.7152777777777779</v>
       </c>
       <c r="E46" s="186"/>
-      <c r="F46" s="462">
+      <c r="F46" s="437">
         <f>$K46/$K43</f>
         <v>0.7603686635944702</v>
       </c>
-      <c r="G46" s="462"/>
-      <c r="H46" s="462"/>
-      <c r="I46" s="462"/>
-      <c r="J46" s="463"/>
+      <c r="G46" s="437"/>
+      <c r="H46" s="437"/>
+      <c r="I46" s="437"/>
+      <c r="J46" s="438"/>
       <c r="K46" s="220">
         <f>SUMIF(M13:M42,"A FAIRE",K13:K42)</f>
         <v>1.7187500000000002</v>
@@ -22860,14 +22937,14 @@
         <v>0.25</v>
       </c>
       <c r="E47" s="187"/>
-      <c r="F47" s="464">
+      <c r="F47" s="439">
         <f>K47/K43</f>
         <v>0.11059907834101383</v>
       </c>
-      <c r="G47" s="464"/>
-      <c r="H47" s="464"/>
-      <c r="I47" s="464"/>
-      <c r="J47" s="465"/>
+      <c r="G47" s="439"/>
+      <c r="H47" s="439"/>
+      <c r="I47" s="439"/>
+      <c r="J47" s="440"/>
       <c r="K47" s="204">
         <f>SUMIF(M13:M42,"EN COURS",K13:K42)</f>
         <v>0.25</v>
@@ -22886,14 +22963,14 @@
         <v>0.29166666666666663</v>
       </c>
       <c r="E48" s="188"/>
-      <c r="F48" s="466">
+      <c r="F48" s="441">
         <f>K48/K43</f>
         <v>0.12903225806451613</v>
       </c>
-      <c r="G48" s="466"/>
-      <c r="H48" s="466"/>
-      <c r="I48" s="466"/>
-      <c r="J48" s="467"/>
+      <c r="G48" s="441"/>
+      <c r="H48" s="441"/>
+      <c r="I48" s="441"/>
+      <c r="J48" s="442"/>
       <c r="K48" s="221">
         <f>SUMIF(M13:M42,"TERMINE.E",K13:K42)</f>
         <v>0.29166666666666663</v>
@@ -22922,24 +22999,170 @@
   </sheetData>
   <sheetProtection formatColumns="0"/>
   <mergeCells count="206">
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AS7:AU7"/>
-    <mergeCell ref="AV7:AW7"/>
-    <mergeCell ref="AX7:AZ7"/>
-    <mergeCell ref="BW7:BY7"/>
-    <mergeCell ref="BZ7:CA7"/>
-    <mergeCell ref="CB7:CD7"/>
-    <mergeCell ref="CE7:CF7"/>
-    <mergeCell ref="CG7:CI7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AD7:AF7"/>
-    <mergeCell ref="AG7:AH7"/>
-    <mergeCell ref="AI7:AK7"/>
-    <mergeCell ref="AL7:AM7"/>
-    <mergeCell ref="AN7:AP7"/>
+    <mergeCell ref="DD7:DE7"/>
+    <mergeCell ref="DF7:DH7"/>
+    <mergeCell ref="DI7:DJ7"/>
+    <mergeCell ref="BA7:BB7"/>
+    <mergeCell ref="BC7:BE7"/>
+    <mergeCell ref="BF7:BG7"/>
+    <mergeCell ref="BH7:BJ7"/>
+    <mergeCell ref="BK7:BL7"/>
+    <mergeCell ref="BM7:BO7"/>
+    <mergeCell ref="BP7:BQ7"/>
+    <mergeCell ref="BR7:BT7"/>
+    <mergeCell ref="BU7:BV7"/>
+    <mergeCell ref="CJ7:CK7"/>
+    <mergeCell ref="CL7:CN7"/>
+    <mergeCell ref="CO7:CP7"/>
+    <mergeCell ref="CQ7:CS7"/>
+    <mergeCell ref="CT7:CU7"/>
+    <mergeCell ref="CV7:CX7"/>
+    <mergeCell ref="CY7:CZ7"/>
+    <mergeCell ref="DA7:DC7"/>
+    <mergeCell ref="AB8:AC8"/>
+    <mergeCell ref="AG8:AH8"/>
+    <mergeCell ref="AL8:AM8"/>
+    <mergeCell ref="AQ8:AR8"/>
+    <mergeCell ref="AV8:AW8"/>
+    <mergeCell ref="BA8:BB8"/>
+    <mergeCell ref="BF8:BG8"/>
+    <mergeCell ref="BK8:BL8"/>
+    <mergeCell ref="BP8:BQ8"/>
+    <mergeCell ref="BU8:BV8"/>
+    <mergeCell ref="BZ8:CA8"/>
+    <mergeCell ref="CE8:CF8"/>
+    <mergeCell ref="CJ8:CK8"/>
+    <mergeCell ref="CO8:CP8"/>
+    <mergeCell ref="CT8:CU8"/>
+    <mergeCell ref="CY8:CZ8"/>
+    <mergeCell ref="DD8:DE8"/>
+    <mergeCell ref="DI8:DJ8"/>
+    <mergeCell ref="DG11:DG12"/>
+    <mergeCell ref="DH11:DH12"/>
+    <mergeCell ref="DI11:DI12"/>
+    <mergeCell ref="DJ11:DJ12"/>
+    <mergeCell ref="CH11:CH12"/>
+    <mergeCell ref="CI11:CI12"/>
+    <mergeCell ref="CJ11:CJ12"/>
+    <mergeCell ref="CK11:CK12"/>
+    <mergeCell ref="CL11:CL12"/>
+    <mergeCell ref="CM11:CM12"/>
+    <mergeCell ref="CN11:CN12"/>
+    <mergeCell ref="CO11:CO12"/>
+    <mergeCell ref="CP11:CP12"/>
+    <mergeCell ref="CQ11:CQ12"/>
+    <mergeCell ref="CR11:CR12"/>
+    <mergeCell ref="CS11:CS12"/>
+    <mergeCell ref="CT11:CT12"/>
+    <mergeCell ref="CU11:CU12"/>
+    <mergeCell ref="CV11:CV12"/>
+    <mergeCell ref="CW11:CW12"/>
+    <mergeCell ref="DC11:DC12"/>
+    <mergeCell ref="DD11:DD12"/>
+    <mergeCell ref="DE11:DE12"/>
+    <mergeCell ref="DF11:DF12"/>
+    <mergeCell ref="CX11:CX12"/>
+    <mergeCell ref="CY11:CY12"/>
+    <mergeCell ref="CZ11:CZ12"/>
+    <mergeCell ref="DA11:DA12"/>
+    <mergeCell ref="DB11:DB12"/>
+    <mergeCell ref="BY11:BY12"/>
+    <mergeCell ref="BZ11:BZ12"/>
+    <mergeCell ref="CA11:CA12"/>
+    <mergeCell ref="CB11:CB12"/>
+    <mergeCell ref="CC11:CC12"/>
+    <mergeCell ref="CD11:CD12"/>
+    <mergeCell ref="CE11:CE12"/>
+    <mergeCell ref="CF11:CF12"/>
+    <mergeCell ref="CG11:CG12"/>
+    <mergeCell ref="BP11:BP12"/>
+    <mergeCell ref="BQ11:BQ12"/>
+    <mergeCell ref="BR11:BR12"/>
+    <mergeCell ref="BS11:BS12"/>
+    <mergeCell ref="BT11:BT12"/>
+    <mergeCell ref="BU11:BU12"/>
+    <mergeCell ref="BV11:BV12"/>
+    <mergeCell ref="BW11:BW12"/>
+    <mergeCell ref="BX11:BX12"/>
+    <mergeCell ref="BG11:BG12"/>
+    <mergeCell ref="BH11:BH12"/>
+    <mergeCell ref="BI11:BI12"/>
+    <mergeCell ref="BJ11:BJ12"/>
+    <mergeCell ref="BK11:BK12"/>
+    <mergeCell ref="BL11:BL12"/>
+    <mergeCell ref="BM11:BM12"/>
+    <mergeCell ref="BN11:BN12"/>
+    <mergeCell ref="BO11:BO12"/>
+    <mergeCell ref="AX11:AX12"/>
+    <mergeCell ref="AY11:AY12"/>
+    <mergeCell ref="AZ11:AZ12"/>
+    <mergeCell ref="BA11:BA12"/>
+    <mergeCell ref="BB11:BB12"/>
+    <mergeCell ref="BC11:BC12"/>
+    <mergeCell ref="BD11:BD12"/>
+    <mergeCell ref="BE11:BE12"/>
+    <mergeCell ref="BF11:BF12"/>
+    <mergeCell ref="V4:Z4"/>
+    <mergeCell ref="V6:Z6"/>
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:X7"/>
+    <mergeCell ref="W8:X8"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="AS10:AW10"/>
+    <mergeCell ref="AX10:BB10"/>
+    <mergeCell ref="BC10:BG10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="E10:I10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="AF11:AF12"/>
+    <mergeCell ref="AG11:AG12"/>
+    <mergeCell ref="AH11:AH12"/>
+    <mergeCell ref="AI11:AI12"/>
+    <mergeCell ref="AJ11:AJ12"/>
+    <mergeCell ref="AK11:AK12"/>
+    <mergeCell ref="AL11:AL12"/>
+    <mergeCell ref="AM11:AM12"/>
+    <mergeCell ref="AN11:AN12"/>
+    <mergeCell ref="AO11:AO12"/>
+    <mergeCell ref="AP11:AP12"/>
+    <mergeCell ref="AQ11:AQ12"/>
+    <mergeCell ref="AS11:AS12"/>
+    <mergeCell ref="AT11:AT12"/>
+    <mergeCell ref="AU11:AU12"/>
+    <mergeCell ref="AV11:AV12"/>
+    <mergeCell ref="AW11:AW12"/>
+    <mergeCell ref="DA9:DE9"/>
+    <mergeCell ref="DF9:DJ9"/>
+    <mergeCell ref="BH10:BL10"/>
+    <mergeCell ref="BM10:BQ10"/>
+    <mergeCell ref="BR10:BV10"/>
+    <mergeCell ref="BW10:CA10"/>
+    <mergeCell ref="CB10:CF10"/>
+    <mergeCell ref="CG10:CK10"/>
+    <mergeCell ref="CL10:CP10"/>
+    <mergeCell ref="CQ10:CU10"/>
+    <mergeCell ref="CV10:CZ10"/>
+    <mergeCell ref="DA10:DE10"/>
+    <mergeCell ref="DF10:DJ10"/>
+    <mergeCell ref="CV9:CZ9"/>
+    <mergeCell ref="CL9:CP9"/>
+    <mergeCell ref="CQ9:CU9"/>
+    <mergeCell ref="AS9:AW9"/>
+    <mergeCell ref="AX9:BB9"/>
+    <mergeCell ref="BC9:BG9"/>
+    <mergeCell ref="BH9:BL9"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="BR9:BV9"/>
+    <mergeCell ref="BW9:CA9"/>
+    <mergeCell ref="CB9:CF9"/>
+    <mergeCell ref="CG9:CK9"/>
     <mergeCell ref="F46:J46"/>
     <mergeCell ref="F47:J47"/>
     <mergeCell ref="F48:J48"/>
@@ -22964,170 +23187,24 @@
     <mergeCell ref="AD11:AD12"/>
     <mergeCell ref="AE11:AE12"/>
     <mergeCell ref="AR11:AR12"/>
-    <mergeCell ref="AS9:AW9"/>
-    <mergeCell ref="AX9:BB9"/>
-    <mergeCell ref="BC9:BG9"/>
-    <mergeCell ref="BH9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BR9:BV9"/>
-    <mergeCell ref="BW9:CA9"/>
-    <mergeCell ref="CB9:CF9"/>
-    <mergeCell ref="CG9:CK9"/>
-    <mergeCell ref="DA9:DE9"/>
-    <mergeCell ref="DF9:DJ9"/>
-    <mergeCell ref="BH10:BL10"/>
-    <mergeCell ref="BM10:BQ10"/>
-    <mergeCell ref="BR10:BV10"/>
-    <mergeCell ref="BW10:CA10"/>
-    <mergeCell ref="CB10:CF10"/>
-    <mergeCell ref="CG10:CK10"/>
-    <mergeCell ref="CL10:CP10"/>
-    <mergeCell ref="CQ10:CU10"/>
-    <mergeCell ref="CV10:CZ10"/>
-    <mergeCell ref="DA10:DE10"/>
-    <mergeCell ref="DF10:DJ10"/>
-    <mergeCell ref="CV9:CZ9"/>
-    <mergeCell ref="CL9:CP9"/>
-    <mergeCell ref="CQ9:CU9"/>
-    <mergeCell ref="AS10:AW10"/>
-    <mergeCell ref="AX10:BB10"/>
-    <mergeCell ref="BC10:BG10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="E10:I10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="AF11:AF12"/>
-    <mergeCell ref="AG11:AG12"/>
-    <mergeCell ref="AH11:AH12"/>
-    <mergeCell ref="AI11:AI12"/>
-    <mergeCell ref="AJ11:AJ12"/>
-    <mergeCell ref="AK11:AK12"/>
-    <mergeCell ref="AL11:AL12"/>
-    <mergeCell ref="AM11:AM12"/>
-    <mergeCell ref="AN11:AN12"/>
-    <mergeCell ref="AO11:AO12"/>
-    <mergeCell ref="AP11:AP12"/>
-    <mergeCell ref="AQ11:AQ12"/>
-    <mergeCell ref="AS11:AS12"/>
-    <mergeCell ref="AT11:AT12"/>
-    <mergeCell ref="AU11:AU12"/>
-    <mergeCell ref="AV11:AV12"/>
-    <mergeCell ref="AW11:AW12"/>
-    <mergeCell ref="V4:Z4"/>
-    <mergeCell ref="V6:Z6"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="W7:X7"/>
-    <mergeCell ref="W8:X8"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="X11:X12"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="AX11:AX12"/>
-    <mergeCell ref="AY11:AY12"/>
-    <mergeCell ref="AZ11:AZ12"/>
-    <mergeCell ref="BA11:BA12"/>
-    <mergeCell ref="BB11:BB12"/>
-    <mergeCell ref="BC11:BC12"/>
-    <mergeCell ref="BD11:BD12"/>
-    <mergeCell ref="BE11:BE12"/>
-    <mergeCell ref="BF11:BF12"/>
-    <mergeCell ref="BG11:BG12"/>
-    <mergeCell ref="BH11:BH12"/>
-    <mergeCell ref="BI11:BI12"/>
-    <mergeCell ref="BJ11:BJ12"/>
-    <mergeCell ref="BK11:BK12"/>
-    <mergeCell ref="BL11:BL12"/>
-    <mergeCell ref="BM11:BM12"/>
-    <mergeCell ref="BN11:BN12"/>
-    <mergeCell ref="BO11:BO12"/>
-    <mergeCell ref="BP11:BP12"/>
-    <mergeCell ref="BQ11:BQ12"/>
-    <mergeCell ref="BR11:BR12"/>
-    <mergeCell ref="BS11:BS12"/>
-    <mergeCell ref="BT11:BT12"/>
-    <mergeCell ref="BU11:BU12"/>
-    <mergeCell ref="BV11:BV12"/>
-    <mergeCell ref="BW11:BW12"/>
-    <mergeCell ref="BX11:BX12"/>
-    <mergeCell ref="CX11:CX12"/>
-    <mergeCell ref="CY11:CY12"/>
-    <mergeCell ref="CZ11:CZ12"/>
-    <mergeCell ref="DA11:DA12"/>
-    <mergeCell ref="DB11:DB12"/>
-    <mergeCell ref="BY11:BY12"/>
-    <mergeCell ref="BZ11:BZ12"/>
-    <mergeCell ref="CA11:CA12"/>
-    <mergeCell ref="CB11:CB12"/>
-    <mergeCell ref="CC11:CC12"/>
-    <mergeCell ref="CD11:CD12"/>
-    <mergeCell ref="CE11:CE12"/>
-    <mergeCell ref="CF11:CF12"/>
-    <mergeCell ref="CG11:CG12"/>
-    <mergeCell ref="DG11:DG12"/>
-    <mergeCell ref="DH11:DH12"/>
-    <mergeCell ref="DI11:DI12"/>
-    <mergeCell ref="DJ11:DJ12"/>
-    <mergeCell ref="CH11:CH12"/>
-    <mergeCell ref="CI11:CI12"/>
-    <mergeCell ref="CJ11:CJ12"/>
-    <mergeCell ref="CK11:CK12"/>
-    <mergeCell ref="CL11:CL12"/>
-    <mergeCell ref="CM11:CM12"/>
-    <mergeCell ref="CN11:CN12"/>
-    <mergeCell ref="CO11:CO12"/>
-    <mergeCell ref="CP11:CP12"/>
-    <mergeCell ref="CQ11:CQ12"/>
-    <mergeCell ref="CR11:CR12"/>
-    <mergeCell ref="CS11:CS12"/>
-    <mergeCell ref="CT11:CT12"/>
-    <mergeCell ref="CU11:CU12"/>
-    <mergeCell ref="CV11:CV12"/>
-    <mergeCell ref="CW11:CW12"/>
-    <mergeCell ref="DC11:DC12"/>
-    <mergeCell ref="DD11:DD12"/>
-    <mergeCell ref="DE11:DE12"/>
-    <mergeCell ref="DF11:DF12"/>
-    <mergeCell ref="BU8:BV8"/>
-    <mergeCell ref="BZ8:CA8"/>
-    <mergeCell ref="CE8:CF8"/>
-    <mergeCell ref="CJ8:CK8"/>
-    <mergeCell ref="CO8:CP8"/>
-    <mergeCell ref="CT8:CU8"/>
-    <mergeCell ref="CY8:CZ8"/>
-    <mergeCell ref="DD8:DE8"/>
-    <mergeCell ref="DI8:DJ8"/>
-    <mergeCell ref="AB8:AC8"/>
-    <mergeCell ref="AG8:AH8"/>
-    <mergeCell ref="AL8:AM8"/>
-    <mergeCell ref="AQ8:AR8"/>
-    <mergeCell ref="AV8:AW8"/>
-    <mergeCell ref="BA8:BB8"/>
-    <mergeCell ref="BF8:BG8"/>
-    <mergeCell ref="BK8:BL8"/>
-    <mergeCell ref="BP8:BQ8"/>
-    <mergeCell ref="DD7:DE7"/>
-    <mergeCell ref="DF7:DH7"/>
-    <mergeCell ref="DI7:DJ7"/>
-    <mergeCell ref="BA7:BB7"/>
-    <mergeCell ref="BC7:BE7"/>
-    <mergeCell ref="BF7:BG7"/>
-    <mergeCell ref="BH7:BJ7"/>
-    <mergeCell ref="BK7:BL7"/>
-    <mergeCell ref="BM7:BO7"/>
-    <mergeCell ref="BP7:BQ7"/>
-    <mergeCell ref="BR7:BT7"/>
-    <mergeCell ref="BU7:BV7"/>
-    <mergeCell ref="CJ7:CK7"/>
-    <mergeCell ref="CL7:CN7"/>
-    <mergeCell ref="CO7:CP7"/>
-    <mergeCell ref="CQ7:CS7"/>
-    <mergeCell ref="CT7:CU7"/>
-    <mergeCell ref="CV7:CX7"/>
-    <mergeCell ref="CY7:CZ7"/>
-    <mergeCell ref="DA7:DC7"/>
+    <mergeCell ref="R7:S7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AD7:AF7"/>
+    <mergeCell ref="AG7:AH7"/>
+    <mergeCell ref="AI7:AK7"/>
+    <mergeCell ref="AL7:AM7"/>
+    <mergeCell ref="AN7:AP7"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AS7:AU7"/>
+    <mergeCell ref="AV7:AW7"/>
+    <mergeCell ref="AX7:AZ7"/>
+    <mergeCell ref="BW7:BY7"/>
+    <mergeCell ref="BZ7:CA7"/>
+    <mergeCell ref="CB7:CD7"/>
+    <mergeCell ref="CE7:CF7"/>
+    <mergeCell ref="CG7:CI7"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A13:L42">
@@ -23307,7 +23384,7 @@
     <col min="13" max="13" width="5.5" customWidth="1"/>
     <col min="14" max="14" width="17.5" customWidth="1"/>
     <col min="15" max="15" width="5.83203125" style="45" customWidth="1"/>
-    <col min="16" max="16" width="30" customWidth="1"/>
+    <col min="16" max="16" width="33.5" customWidth="1"/>
     <col min="17" max="17" width="107.83203125" customWidth="1"/>
     <col min="18" max="18" width="10.5" customWidth="1"/>
     <col min="20" max="20" width="47.6640625" customWidth="1"/>
@@ -23365,7 +23442,7 @@
       </c>
       <c r="L2" s="64">
         <f>SUM(K4:K26)</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="O2" s="19" t="s">
         <v>140</v>
@@ -23643,30 +23720,44 @@
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="107"/>
-      <c r="B8" s="308"/>
-      <c r="C8" s="309"/>
-      <c r="D8" s="310"/>
-      <c r="E8" s="46" t="str">
+      <c r="B8" s="308">
+        <v>46295</v>
+      </c>
+      <c r="C8" s="309">
+        <v>0.34722222222222221</v>
+      </c>
+      <c r="D8" s="310">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="E8" s="46">
         <f t="shared" si="0"/>
-        <v/>
+        <v>7.6388888888888895E-2</v>
       </c>
       <c r="F8" s="314"/>
-      <c r="G8" s="315"/>
+      <c r="G8" s="315" t="s">
+        <v>230</v>
+      </c>
       <c r="H8" s="315"/>
       <c r="I8" s="315"/>
       <c r="J8" s="316"/>
-      <c r="K8" s="109" t="str">
+      <c r="K8" s="109">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L8" s="318"/>
+        <v>7.6388888888888895E-2</v>
+      </c>
+      <c r="L8" s="318" t="s">
+        <v>227</v>
+      </c>
       <c r="M8" s="5" t="str">
         <f>IF(ISBLANK(L8),"",HLOOKUP(L8,Suivi!A$5:T$6,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N8" s="323"/>
+        <v>TP_1</v>
+      </c>
+      <c r="N8" s="323" t="s">
+        <v>271</v>
+      </c>
       <c r="O8" s="324"/>
-      <c r="P8" s="325"/>
+      <c r="P8" s="325" t="s">
+        <v>272</v>
+      </c>
       <c r="Q8" s="326"/>
       <c r="R8" s="325"/>
       <c r="S8" s="104"/>
@@ -23677,28 +23768,40 @@
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="107"/>
-      <c r="B9" s="308"/>
-      <c r="C9" s="309"/>
-      <c r="D9" s="310"/>
-      <c r="E9" s="46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="B9" s="308">
+        <v>46295</v>
+      </c>
+      <c r="C9" s="309">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D9" s="310">
+        <v>0.4375</v>
+      </c>
+      <c r="E9" s="46">
+        <f t="shared" ref="E9:E10" si="2">IF(ISBLANK(D9),"",D9-C9)</f>
+        <v>6.9444444444444198E-3</v>
       </c>
       <c r="F9" s="314"/>
-      <c r="G9" s="315"/>
+      <c r="G9" s="315" t="s">
+        <v>230</v>
+      </c>
       <c r="H9" s="315"/>
       <c r="I9" s="315"/>
       <c r="J9" s="316"/>
-      <c r="K9" s="109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L9" s="318"/>
+      <c r="K9" s="109">
+        <f t="shared" ref="K9:K10" si="3">IF(AND(ISBLANK(F9),ISBLANK(G9),ISBLANK(H9),ISBLANK(I9),ISBLANK(J9)),"",COUNTIF(F9:J9,"x")*E9)</f>
+        <v>6.9444444444444198E-3</v>
+      </c>
+      <c r="L9" s="318" t="s">
+        <v>227</v>
+      </c>
       <c r="M9" s="5" t="str">
         <f>IF(ISBLANK(L9),"",HLOOKUP(L9,Suivi!A$5:T$6,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N9" s="323"/>
+        <v>TP_1</v>
+      </c>
+      <c r="N9" s="323" t="s">
+        <v>228</v>
+      </c>
       <c r="O9" s="324"/>
       <c r="P9" s="325"/>
       <c r="Q9" s="326"/>
@@ -23711,30 +23814,44 @@
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="107"/>
-      <c r="B10" s="308"/>
-      <c r="C10" s="309"/>
-      <c r="D10" s="310"/>
-      <c r="E10" s="46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="B10" s="308">
+        <v>46295</v>
+      </c>
+      <c r="C10" s="309">
+        <v>0.44097222222222221</v>
+      </c>
+      <c r="D10" s="310">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="E10" s="46">
+        <f t="shared" si="2"/>
+        <v>1.3194444444444453E-2</v>
       </c>
       <c r="F10" s="314"/>
-      <c r="G10" s="315"/>
+      <c r="G10" s="315" t="s">
+        <v>230</v>
+      </c>
       <c r="H10" s="315"/>
       <c r="I10" s="315"/>
       <c r="J10" s="316"/>
-      <c r="K10" s="109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L10" s="318"/>
+      <c r="K10" s="109">
+        <f t="shared" si="3"/>
+        <v>1.3194444444444453E-2</v>
+      </c>
+      <c r="L10" s="318" t="s">
+        <v>227</v>
+      </c>
       <c r="M10" s="5" t="str">
         <f>IF(ISBLANK(L10),"",HLOOKUP(L10,Suivi!A$5:T$6,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N10" s="323"/>
+        <v>TP_1</v>
+      </c>
+      <c r="N10" s="323" t="s">
+        <v>271</v>
+      </c>
       <c r="O10" s="324"/>
-      <c r="P10" s="325"/>
+      <c r="P10" s="325" t="s">
+        <v>273</v>
+      </c>
       <c r="Q10" s="326"/>
       <c r="R10" s="325"/>
       <c r="S10" s="104"/>
@@ -23744,38 +23861,50 @@
       <c r="W10" s="330"/>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A11" s="107"/>
-      <c r="B11" s="308"/>
-      <c r="C11" s="309"/>
-      <c r="D11" s="310"/>
-      <c r="E11" s="46" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="F11" s="314"/>
-      <c r="G11" s="315"/>
-      <c r="H11" s="315"/>
-      <c r="I11" s="315"/>
-      <c r="J11" s="316"/>
-      <c r="K11" s="109" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="L11" s="318"/>
+      <c r="A11" s="470"/>
+      <c r="B11" s="471" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="472">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D11" s="473">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E11" s="474">
+        <v>7.6388888888888895E-2</v>
+      </c>
+      <c r="F11" s="475"/>
+      <c r="G11" s="476" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="476"/>
+      <c r="I11" s="476"/>
+      <c r="J11" s="477"/>
+      <c r="K11" s="478">
+        <v>7.6388888888888895E-2</v>
+      </c>
+      <c r="L11" s="318" t="s">
+        <v>241</v>
+      </c>
       <c r="M11" s="5" t="str">
         <f>IF(ISBLANK(L11),"",HLOOKUP(L11,Suivi!A$5:T$6,2,FALSE))</f>
-        <v/>
-      </c>
-      <c r="N11" s="323"/>
-      <c r="O11" s="324"/>
-      <c r="P11" s="325"/>
-      <c r="Q11" s="326"/>
-      <c r="R11" s="325"/>
-      <c r="S11" s="104"/>
-      <c r="T11" s="308"/>
-      <c r="U11" s="308"/>
-      <c r="V11" s="329"/>
-      <c r="W11" s="330"/>
+        <v>TP_3</v>
+      </c>
+      <c r="N11" s="323" t="s">
+        <v>275</v>
+      </c>
+      <c r="O11" s="480"/>
+      <c r="P11" s="481" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q11" s="482"/>
+      <c r="R11" s="481"/>
+      <c r="S11" s="483"/>
+      <c r="T11" s="471"/>
+      <c r="U11" s="471"/>
+      <c r="V11" s="484"/>
+      <c r="W11" s="479"/>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="107"/>
@@ -24289,7 +24418,7 @@
       </c>
       <c r="G27" s="59">
         <f>SUMIF(G4:G26,"x",$E4:$E26)</f>
-        <v>0.27083333333333343</v>
+        <v>0.44375000000000009</v>
       </c>
       <c r="H27" s="59">
         <f>SUMIF(H4:H26,"x",$E4:$E26)</f>
@@ -24305,7 +24434,7 @@
       </c>
       <c r="K27" s="57">
         <f>SUM(K4:K26)</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="L27" s="55" t="s">
         <v>159</v>
@@ -24327,7 +24456,7 @@
       <c r="M28" s="55"/>
       <c r="N28" s="191">
         <f>K27-N27</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="O28" s="22">
         <f>IF(N28&gt;0,N28/K27,"0 %")</f>
@@ -24335,7 +24464,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" formatColumns="0"/>
+  <sheetProtection formatColumns="0"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1:W3 W27:W1048576" xr:uid="{BAA2B023-E3AC-4D69-9614-B172B30F8CD1}">
@@ -24435,7 +24564,7 @@
       </c>
       <c r="I4" s="412">
         <f>B22+D22+F22+H22+J22+L22+N22+P22+R22+T22</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="J4" s="410" t="s">
         <v>163</v>
@@ -24593,7 +24722,7 @@
       </c>
       <c r="B8" s="11">
         <f>IF(ISBLANK(A8),"",SUMIF('Journal de bord'!N:N,A8,'Journal de bord'!K:K))</f>
-        <v>8.9583333333333348E-2</v>
+        <v>9.6527777777777768E-2</v>
       </c>
       <c r="C8" s="331" t="s">
         <v>233</v>
@@ -24716,10 +24845,12 @@
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="318"/>
-      <c r="B10" s="11" t="str">
+      <c r="A10" s="318" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="11">
         <f>IF(ISBLANK(A10),"",SUMIF('Journal de bord'!N:N,A10,'Journal de bord'!K:K))</f>
-        <v/>
+        <v>8.9583333333333348E-2</v>
       </c>
       <c r="C10" s="318" t="s">
         <v>236</v>
@@ -25110,10 +25241,12 @@
         <f>IF(ISBLANK(C17),"",SUMIF('Journal de bord'!N:N,C17,'Journal de bord'!K:K))</f>
         <v/>
       </c>
-      <c r="E17" s="318"/>
-      <c r="F17" s="9" t="str">
+      <c r="E17" s="318" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="9">
         <f>IF(ISBLANK(E17),"",SUMIF('Journal de bord'!N:N,E17,'Journal de bord'!K:K))</f>
-        <v/>
+        <v>7.6388888888888895E-2</v>
       </c>
       <c r="G17" s="318"/>
       <c r="H17" s="9" t="str">
@@ -25368,7 +25501,7 @@
       </c>
       <c r="B22" s="14">
         <f>SUM(B8:B21)</f>
-        <v>0.33055555555555566</v>
+        <v>0.42708333333333343</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>97</v>
@@ -25382,7 +25515,7 @@
       </c>
       <c r="F22" s="14">
         <f t="shared" ref="F22" si="1">SUM(F8:F21)</f>
-        <v>0</v>
+        <v>7.6388888888888895E-2</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>97</v>
@@ -25435,7 +25568,7 @@
       </c>
       <c r="U22" s="82">
         <f t="shared" ref="U22" si="9">SUM(B22:T22)</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="V22" t="s">
         <v>175</v>
@@ -25448,7 +25581,7 @@
       </c>
       <c r="B23" s="79">
         <f>IF(B22=0,"",B22/$I4)</f>
-        <v>1</v>
+        <v>0.84827586206896555</v>
       </c>
       <c r="C23" s="78" t="str">
         <f>IF(ISBLANK(C5),"",C5)</f>
@@ -25462,9 +25595,9 @@
         <f>IF(ISBLANK(E5),"",E5)</f>
         <v>Code</v>
       </c>
-      <c r="F23" s="79" t="str">
+      <c r="F23" s="79">
         <f>IF(F22=0,"",F22/$I4)</f>
-        <v/>
+        <v>0.15172413793103445</v>
       </c>
       <c r="G23" s="78" t="str">
         <f>IF(ISBLANK(G5),"",G5)</f>
@@ -25569,15 +25702,15 @@
       </c>
       <c r="B26" s="81">
         <f>IF(B22&gt;B24,B22-B24,"")</f>
-        <v>0.33055555555555566</v>
+        <v>0.42708333333333343</v>
       </c>
       <c r="D26" s="81" t="str">
         <f>IF(D22&gt;D24,D22-D24,"")</f>
         <v/>
       </c>
-      <c r="F26" s="81" t="str">
+      <c r="F26" s="81">
         <f>IF(F22&gt;F24,F22-F24,"")</f>
-        <v/>
+        <v>7.6388888888888895E-2</v>
       </c>
       <c r="H26" s="81" t="str">
         <f>IF(H22&gt;H24,H22-H24,"")</f>
@@ -25609,7 +25742,7 @@
       </c>
       <c r="U26" s="82">
         <f>SUM(B26:T26)</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
@@ -25671,7 +25804,7 @@
       </c>
       <c r="D29" s="85">
         <f>IF(U22&gt;U24,U22-U24,"")</f>
-        <v>0.33055555555555566</v>
+        <v>0.50347222222222232</v>
       </c>
       <c r="E29" s="84" t="s">
         <v>180</v>
@@ -25693,7 +25826,7 @@
       </c>
       <c r="B32" s="71">
         <f>B23</f>
-        <v>1</v>
+        <v>0.84827586206896555</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
@@ -25711,9 +25844,9 @@
         <f>E23</f>
         <v>Code</v>
       </c>
-      <c r="B34" s="73" t="str">
+      <c r="B34" s="73">
         <f>F23</f>
-        <v/>
+        <v>0.15172413793103445</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
@@ -26065,15 +26198,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010010C4EC33272888438EF03C347CBC4CB7" ma:contentTypeVersion="11" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="2073dadaf97adf825068798ae6f37fc6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ae7e04d0-6b12-4d3b-9f8a-75c44f8e1194" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a520961d0fbcfb65403c33e2efd42a1a" ns2:_="">
     <xsd:import namespace="ae7e04d0-6b12-4d3b-9f8a-75c44f8e1194"/>
@@ -26257,6 +26381,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -26268,14 +26401,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9954475-C7B7-4EFD-A780-F74990CA5D07}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13DD2232-303F-4087-A55A-BEC9780E5BC5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -26293,18 +26418,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9954475-C7B7-4EFD-A780-F74990CA5D07}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C59968C-958F-420F-B3BD-87D94183B77C}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ae7e04d0-6b12-4d3b-9f8a-75c44f8e1194"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="ae7e04d0-6b12-4d3b-9f8a-75c44f8e1194"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>